--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EVAL\1_PrestaShop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622B6FB9-F48F-47D7-A456-90AD91412A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCCB237-5D75-46F9-83C9-4E2A7E513164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="141">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -411,6 +411,45 @@
   </si>
   <si>
     <t>fonction filtre de produits selon criteres</t>
+  </si>
+  <si>
+    <t>auth-api.js</t>
+  </si>
+  <si>
+    <t>product-api.js</t>
+  </si>
+  <si>
+    <t>Fonction de gestion d'erreur  de fichier</t>
+  </si>
+  <si>
+    <t>Mise a jour d'interface pour les logs</t>
+  </si>
+  <si>
+    <t>Gestion de stock</t>
+  </si>
+  <si>
+    <t>StockManager.vue</t>
+  </si>
+  <si>
+    <t>stock-api.js</t>
+  </si>
+  <si>
+    <t>Fonction de mouvements de stock</t>
+  </si>
+  <si>
+    <t>Amelioration d'interface (petite dashboard d'evolution)</t>
+  </si>
+  <si>
+    <t>Fonction filtre selon date et mouvement</t>
+  </si>
+  <si>
+    <t>Ajout champ information stock disponible</t>
+  </si>
+  <si>
+    <t>Get et Affichage de stock dispo</t>
+  </si>
+  <si>
+    <t>Fonction de get de stock disponible</t>
   </si>
 </sst>
 </file>
@@ -749,9 +788,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46157.311128935187" refreshedVersion="8" recordCount="46" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46157.637541203701" refreshedVersion="8" recordCount="71" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B1:K1008" sheet="liste des taches"/>
+    <worksheetSource ref="B1:K1007" sheet="liste des taches"/>
   </cacheSource>
   <cacheFields count="10">
     <cacheField name="Catégorie" numFmtId="0">
@@ -804,7 +843,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="46">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="71">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -832,7 +871,7 @@
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
-    <s v="prestashop-api.js"/>
+    <s v="auth-api.js"/>
     <s v="checkLogin"/>
     <s v="Metier"/>
     <x v="0"/>
@@ -951,9 +990,9 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Product"/>
     <s v="ProductImport.service.ts"/>
-    <s v="fonction calculatePrixHt"/>
+    <s v="fonction calculatePrix Ht"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -963,9 +1002,9 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Product"/>
     <s v="ProductImport.service.ts"/>
-    <s v="fonction getTaxGroupId"/>
+    <s v="fonction obtention group de taxe"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -975,9 +1014,9 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Product"/>
     <s v="ProductImport.service.ts"/>
-    <s v="fonction buildProductXml"/>
+    <s v="fonction de build de xml de produit"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -987,9 +1026,9 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Product"/>
     <s v="ProductImport.service.ts"/>
-    <s v="fonction runImport"/>
+    <s v="fonction runProductImport"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -999,7 +1038,19 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Product"/>
+    <s v="ProductLoadCsv.ts"/>
+    <s v="Chargement csv en data[]"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Combination"/>
     <s v="CombinationImport.service.ts"/>
     <s v="fonction getDynamicTaxRate"/>
     <s v="Metier"/>
@@ -1011,7 +1062,7 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Combination"/>
     <s v="CombinationImport.service.ts"/>
     <s v="fonction ensureAttrAndVal"/>
     <s v="Metier"/>
@@ -1023,7 +1074,7 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Combination"/>
     <s v="CombinationImport.service.ts"/>
     <s v="fonction setStock"/>
     <s v="Metier"/>
@@ -1035,7 +1086,7 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Combination"/>
     <s v="CombinationImport.service.ts"/>
     <s v="fonction runCombinationImport"/>
     <s v="Metier"/>
@@ -1047,9 +1098,57 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Combination"/>
+    <s v="CombinationLoadCsv.ts"/>
+    <s v="Chargement csv en data[]"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Order"/>
+    <s v="OrderImport.ts"/>
+    <s v="fonction gestion customer: find /create"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Order"/>
+    <s v="OrderImport.ts"/>
+    <s v="fonction mapping Etat Order et Payent"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Order"/>
+    <s v="OrderImport.ts"/>
+    <s v="fonction gestion customer: find /create"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Order"/>
     <s v="OrderImport.service.ts"/>
-    <s v="fonction"/>
+    <s v="fonction gestion panier find/create"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -1059,9 +1158,9 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Order"/>
     <s v="OrderImport.service.ts"/>
-    <s v="fonction"/>
+    <s v="fonction payement et ajout dans panier"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -1071,9 +1170,9 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Order"/>
     <s v="OrderImport.service.ts"/>
-    <s v="fonction"/>
+    <s v="fonction creation commande, et maj"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -1083,10 +1182,46 @@
   </r>
   <r>
     <s v="Backoffice"/>
-    <s v="Gestion Import"/>
+    <s v="Gestion Import Order"/>
     <s v="OrderImport.service.ts"/>
-    <s v="fonction"/>
+    <s v="fonction runOrderImport"/>
     <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Order"/>
+    <s v="OrderLoadCsv.ts"/>
+    <s v="Chargement csv en data[]"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Image"/>
+    <s v="correspondanceImage.ts"/>
+    <s v="cherche nom_fichier % ref de produit"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Image"/>
+    <s v="ImageImport.service.ts"/>
+    <s v="dezip et mise a jour image dans prestashop"/>
+    <s v="Integration"/>
     <x v="0"/>
     <n v="100"/>
     <n v="100"/>
@@ -1109,20 +1244,8 @@
     <s v="Backoffice"/>
     <s v="Gestion Import"/>
     <s v="Import.vue"/>
-    <s v="load csv"/>
+    <s v="Script d'integration"/>
     <s v="Integration"/>
-    <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion Import"/>
-    <s v="Import.vue"/>
-    <s v="fonctions d'insertions des images"/>
-    <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
     <n v="100"/>
@@ -1144,7 +1267,7 @@
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Commande"/>
-    <s v="prestashop-api.js"/>
+    <s v="product-api.js"/>
     <s v="Modification Etat , psUpdateOrderState"/>
     <s v="Metier"/>
     <x v="0"/>
@@ -1216,7 +1339,7 @@
   <r>
     <s v="FrontOffice"/>
     <s v="Accueil,gestion produits"/>
-    <s v="prestashop-api.js"/>
+    <s v="product-api.js"/>
     <s v="fonctions product_feature_values"/>
     <s v="Metier"/>
     <x v="0"/>
@@ -1228,7 +1351,7 @@
   <r>
     <s v="FrontOffice"/>
     <s v="Accueil,gestion produits"/>
-    <s v="prestashop-api.js"/>
+    <s v="product-api.js"/>
     <s v="fonctions product_option_values"/>
     <s v="Metier"/>
     <x v="0"/>
@@ -1240,7 +1363,7 @@
   <r>
     <s v="FrontOffice"/>
     <s v="Accueil,gestion produits"/>
-    <s v="prestashop-api.js"/>
+    <s v="product-api.js"/>
     <s v="fonctions combinations"/>
     <s v="Metier"/>
     <x v="0"/>
@@ -1252,7 +1375,7 @@
   <r>
     <s v="FrontOffice"/>
     <s v="Accueil,gestion produits"/>
-    <s v="prestashop-api.js"/>
+    <s v="product-api.js"/>
     <s v="fonctions psGetProductFullDetails"/>
     <s v="Metier"/>
     <x v="0"/>
@@ -1288,8 +1411,8 @@
   <r>
     <s v="FrontOffice"/>
     <s v="Gestion Panier"/>
-    <s v="prestashop-api.js"/>
-    <s v="fonction psGetCartSecureKey"/>
+    <s v="product-api.js"/>
+    <s v="fonction get cle de panier"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -1300,8 +1423,8 @@
   <r>
     <s v="FrontOffice"/>
     <s v="Gestion Panier"/>
-    <s v="prestashop-api.js"/>
-    <s v="fonction cart , psCreateCart"/>
+    <s v="product-api.js"/>
+    <s v="fonction gestion panier find/create"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -1311,9 +1434,9 @@
   </r>
   <r>
     <s v="FrontOffice"/>
-    <s v="Gestion Panier"/>
-    <s v="prestashop-api.js"/>
-    <s v="fonction psCreateOrder"/>
+    <s v="Gestion Achat"/>
+    <s v="product-api.js"/>
+    <s v="fonction creation commande, et maj"/>
     <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
@@ -1323,7 +1446,7 @@
   </r>
   <r>
     <s v="FrontOffice"/>
-    <s v="Gestion Panier"/>
+    <s v="Gestion Achat"/>
     <s v="Cart.vue"/>
     <s v="Script d'integration"/>
     <s v="Integration"/>
@@ -1335,10 +1458,226 @@
   </r>
   <r>
     <s v="FrontOffice"/>
-    <s v="Gestion Panier"/>
-    <s v="Cart.vue"/>
-    <m/>
-    <m/>
+    <s v="Gestion Commande"/>
+    <s v="OrderList.vue"/>
+    <s v="Creation interface"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Commande"/>
+    <s v="OrderList.vue"/>
+    <s v="Script d'integration chargement Etat"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Etat Commande"/>
+    <s v="OrderList.vue"/>
+    <s v="Creation interface"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Etat Commande"/>
+    <s v="OrderList.vue"/>
+    <s v="Script d'integration"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Etat Commande"/>
+    <s v="product-api.js"/>
+    <s v="Integration de panier ey mise a jour Etat Commande"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Tableau de bord"/>
+    <s v="Home.vue"/>
+    <s v="Creation interface"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Tableau de bord"/>
+    <s v="product-api.js"/>
+    <s v="load des commandes by date et calcul des amount "/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Tableau de bord"/>
+    <s v="Home.vue"/>
+    <s v="Script d'integration"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Route"/>
+    <s v="App.vue"/>
+    <s v="mise a jour de currentPage pour choix utilisateur"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Route"/>
+    <s v="App.vue"/>
+    <s v="gestion et protection pages pour iutilisateur anonym"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Utilisateur"/>
+    <s v="UserPick.vue"/>
+    <s v="Creation interface"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Utilisateur"/>
+    <s v="auth-api.js"/>
+    <s v="Get tous les comptes utilisateurs"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Utilisateur"/>
+    <s v="auth-api.js"/>
+    <s v="Fontion de login dynamique selon user choisies"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Utilisateur"/>
+    <s v="UserPick.vue"/>
+    <s v="Script d'integration"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produit"/>
+    <s v="Home.vue"/>
+    <s v="Mise a jour interface"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produit"/>
+    <s v="product-api.js"/>
+    <s v="fonction de gestion de badge selon date availability"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produit"/>
+    <s v="Home.vue"/>
+    <s v="Script d'integration"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produit"/>
+    <s v="Home.vue"/>
+    <s v="Mise a jour interface ajout filtre"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion Produit"/>
+    <s v="Home.vue"/>
+    <s v="fonction filtre de produits selon criteres"/>
+    <s v="Metier"/>
     <x v="0"/>
     <n v="100"/>
     <n v="100"/>
@@ -1676,7 +2015,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1806,7 +2145,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>22</v>
@@ -1898,7 +2237,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" ref="J6:J48" si="2">H6-I6</f>
+        <f t="shared" ref="J6:J14" si="2">H6-I6</f>
         <v>0</v>
       </c>
       <c r="K6" s="9">
@@ -3027,7 +3366,7 @@
         <v>47</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>52</v>
@@ -3249,7 +3588,7 @@
         <v>56</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>58</v>
@@ -3286,7 +3625,7 @@
         <v>56</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>59</v>
@@ -3323,7 +3662,7 @@
         <v>56</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>60</v>
@@ -3360,7 +3699,7 @@
         <v>56</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>57</v>
@@ -3471,7 +3810,7 @@
         <v>83</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>108</v>
@@ -3508,7 +3847,7 @@
         <v>83</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>91</v>
@@ -3545,7 +3884,7 @@
         <v>109</v>
       </c>
       <c r="D51" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>93</v>
@@ -3767,7 +4106,7 @@
         <v>112</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>113</v>
@@ -3841,7 +4180,7 @@
         <v>114</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>115</v>
@@ -4026,7 +4365,7 @@
         <v>117</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>120</v>
@@ -4063,7 +4402,7 @@
         <v>117</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>121</v>
@@ -4174,7 +4513,7 @@
         <v>123</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>125</v>
@@ -4308,6 +4647,524 @@
       </c>
       <c r="K71" s="9">
         <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="12.75">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H72" s="6">
+        <v>100</v>
+      </c>
+      <c r="I72" s="8">
+        <v>100</v>
+      </c>
+      <c r="J72" s="8">
+        <f t="shared" ref="J72" si="30">H72-I72</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="9">
+        <f t="shared" ref="K72" si="31">(I72/(I72+J72))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="12.75">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H73" s="6">
+        <v>100</v>
+      </c>
+      <c r="I73" s="8">
+        <v>100</v>
+      </c>
+      <c r="J73" s="8">
+        <f t="shared" ref="J73:J74" si="32">H73-I73</f>
+        <v>0</v>
+      </c>
+      <c r="K73" s="9">
+        <f t="shared" ref="K73:K74" si="33">(I73/(I73+J73))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="12.75">
+      <c r="A74" s="5">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D74" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H74" s="6">
+        <v>100</v>
+      </c>
+      <c r="I74" s="8">
+        <v>100</v>
+      </c>
+      <c r="J74" s="8">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="9">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="12.75">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D75" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H75" s="6">
+        <v>100</v>
+      </c>
+      <c r="I75" s="8">
+        <v>100</v>
+      </c>
+      <c r="J75" s="8">
+        <f t="shared" ref="J75" si="34">H75-I75</f>
+        <v>0</v>
+      </c>
+      <c r="K75" s="9">
+        <f t="shared" ref="K75" si="35">(I75/(I75+J75))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="12.75">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H76" s="6">
+        <v>100</v>
+      </c>
+      <c r="I76" s="8">
+        <v>100</v>
+      </c>
+      <c r="J76" s="8">
+        <f t="shared" ref="J76:J80" si="36">H76-I76</f>
+        <v>0</v>
+      </c>
+      <c r="K76" s="9">
+        <f t="shared" ref="K76:K80" si="37">(I76/(I76+J76))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="12.75">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D77" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H77" s="6">
+        <v>100</v>
+      </c>
+      <c r="I77" s="8">
+        <v>100</v>
+      </c>
+      <c r="J77" s="8">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="9">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="12.75">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H78" s="6">
+        <v>100</v>
+      </c>
+      <c r="I78" s="8">
+        <v>100</v>
+      </c>
+      <c r="J78" s="8">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="9">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="12.75">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H79" s="6">
+        <v>100</v>
+      </c>
+      <c r="I79" s="8">
+        <v>100</v>
+      </c>
+      <c r="J79" s="8">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="9">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="12.75">
+      <c r="A80" s="5">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H80" s="6">
+        <v>100</v>
+      </c>
+      <c r="I80" s="8">
+        <v>100</v>
+      </c>
+      <c r="J80" s="8">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="9">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="12.75">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D81" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H81" s="6">
+        <v>100</v>
+      </c>
+      <c r="I81" s="8">
+        <v>100</v>
+      </c>
+      <c r="J81" s="8">
+        <f t="shared" ref="J81:J82" si="38">H81-I81</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="9">
+        <f t="shared" ref="K81:K82" si="39">(I81/(I81+J81))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="12.75">
+      <c r="A82" s="5">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H82" s="6">
+        <v>100</v>
+      </c>
+      <c r="I82" s="8">
+        <v>100</v>
+      </c>
+      <c r="J82" s="8">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="9">
+        <f t="shared" si="39"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="12.75">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D83" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H83" s="6">
+        <v>100</v>
+      </c>
+      <c r="I83" s="8">
+        <v>100</v>
+      </c>
+      <c r="J83" s="8">
+        <f t="shared" ref="J83" si="40">H83-I83</f>
+        <v>0</v>
+      </c>
+      <c r="K83" s="9">
+        <f t="shared" ref="K83" si="41">(I83/(I83+J83))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="12.75">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D84" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H84" s="6">
+        <v>100</v>
+      </c>
+      <c r="I84" s="8">
+        <v>100</v>
+      </c>
+      <c r="J84" s="8">
+        <f t="shared" ref="J84:J85" si="42">H84-I84</f>
+        <v>0</v>
+      </c>
+      <c r="K84" s="9">
+        <f t="shared" ref="K84:K85" si="43">(I84/(I84+J84))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="12.75">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H85" s="6">
+        <v>100</v>
+      </c>
+      <c r="I85" s="8">
+        <v>100</v>
+      </c>
+      <c r="J85" s="8">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="9">
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
     </row>
@@ -4352,10 +5209,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="32">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="C3" s="33">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="D3" s="34">
         <v>0</v>
@@ -4374,10 +5231,10 @@
         <v>36</v>
       </c>
       <c r="B5" s="38">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="C5" s="39">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="D5" s="40">
         <v>0</v>
@@ -4434,11 +5291,11 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="14">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>7000</v>
+        <v>8400</v>
       </c>
       <c r="B2" s="14">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>7000</v>
+        <v>8400</v>
       </c>
       <c r="C2" s="14">
         <f>SUM('liste des taches'!J:J)</f>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EVAL\1_PrestaShop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCCB237-5D75-46F9-83C9-4E2A7E513164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84541F7B-B3C2-4969-8AD7-AE22D0A69CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="141">
-  <si>
-    <t>ETU00XXXX</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="159">
   <si>
     <t>A</t>
   </si>
@@ -266,12 +263,6 @@
     <t>ResetReport.vue</t>
   </si>
   <si>
-    <t>fonction getDynamicTaxRate</t>
-  </si>
-  <si>
-    <t>fonction ensureAttrAndVal</t>
-  </si>
-  <si>
     <t>fonction setStock</t>
   </si>
   <si>
@@ -395,9 +386,6 @@
     <t>Fontion de login dynamique selon user choisies</t>
   </si>
   <si>
-    <t>gestion et protection pages pour iutilisateur anonym</t>
-  </si>
-  <si>
     <t>Gestion Produit</t>
   </si>
   <si>
@@ -434,22 +422,88 @@
     <t>stock-api.js</t>
   </si>
   <si>
-    <t>Fonction de mouvements de stock</t>
-  </si>
-  <si>
-    <t>Amelioration d'interface (petite dashboard d'evolution)</t>
-  </si>
-  <si>
-    <t>Fonction filtre selon date et mouvement</t>
-  </si>
-  <si>
     <t>Ajout champ information stock disponible</t>
   </si>
   <si>
-    <t>Get et Affichage de stock dispo</t>
-  </si>
-  <si>
-    <t>Fonction de get de stock disponible</t>
+    <t>Existing App</t>
+  </si>
+  <si>
+    <t>StockDelta.php</t>
+  </si>
+  <si>
+    <t>ws_stock_update.php</t>
+  </si>
+  <si>
+    <t>Creation du mouvement de stock endpoint</t>
+  </si>
+  <si>
+    <t>Creation Entite du module de stock et endpoint</t>
+  </si>
+  <si>
+    <t>Appelle de l'endpoint mise a jour stockAvailable</t>
+  </si>
+  <si>
+    <t>Appelle de l'endpoint mise a jour stockByDelta</t>
+  </si>
+  <si>
+    <t>Fonction get stock mvt a partir des commandes</t>
+  </si>
+  <si>
+    <t>chargement des stock et maj quantite</t>
+  </si>
+  <si>
+    <t>Ajout option voir evolution et creation modal</t>
+  </si>
+  <si>
+    <t>Appelle  get stock_deltas et psGetStockMovementsFromOrders</t>
+  </si>
+  <si>
+    <t>Interface graphique</t>
+  </si>
+  <si>
+    <t>Activation du module et cle ws stock update via delta</t>
+  </si>
+  <si>
+    <t>Appelle fonction stock_availables</t>
+  </si>
+  <si>
+    <t>Gestion navigation anonym</t>
+  </si>
+  <si>
+    <t>FoUserPick.vue</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>Champ navigation anonym ou guest</t>
+  </si>
+  <si>
+    <t>gestion et protection pages sans authentification</t>
+  </si>
+  <si>
+    <t>Limit du navigation guest jusqua ce que validation achat</t>
+  </si>
+  <si>
+    <t>Creation module d'authentification au moment validation achat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration  authentification avec compte ou creation </t>
+  </si>
+  <si>
+    <t>Chargement des paniers si authentifie avec compte déjà present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation du commande </t>
+  </si>
+  <si>
+    <t>fonction de gestion de declinaisons</t>
+  </si>
+  <si>
+    <t>fonction get dynamique de taux de tax</t>
+  </si>
+  <si>
+    <t>fonction gestion address</t>
   </si>
 </sst>
 </file>
@@ -459,7 +513,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -498,12 +552,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Liberation Serif"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -710,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -725,29 +773,27 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" pivotButton="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -766,6 +812,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,9 +835,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46157.637541203701" refreshedVersion="8" recordCount="71" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46159.800975347222" refreshedVersion="8" recordCount="85" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B1:K1007" sheet="liste des taches"/>
+    <worksheetSource ref="B1:K1006" sheet="liste des taches"/>
   </cacheSource>
   <cacheFields count="10">
     <cacheField name="Catégorie" numFmtId="0">
@@ -843,7 +890,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="71">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="85">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -1678,6 +1725,174 @@
     <s v="Home.vue"/>
     <s v="fonction filtre de produits selon criteres"/>
     <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Product"/>
+    <s v="ProductLoadCsv.ts"/>
+    <s v="Fonction de gestion d'erreur  de fichier"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Combination"/>
+    <s v="CombinationLoadCsv.ts"/>
+    <s v="Fonction de gestion d'erreur  de fichier"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import Order"/>
+    <s v="OrderLoadCsv.ts"/>
+    <s v="Fonction de gestion d'erreur  de fichier"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion Import"/>
+    <s v="Import.vue"/>
+    <s v="Mise a jour d'interface pour les logs"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="StockManager.vue"/>
+    <s v="Creation interface"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="stock-api.js"/>
+    <s v="Fonction de mouvements de stock"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="StockManager.vue"/>
+    <s v="Script d'integration"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="StockManager.vue"/>
+    <s v="Amelioration d'interface (petite dashboard d'evolution)"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="stock-api.js"/>
+    <s v="Fonction filtre selon date et mouvement"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="StockManager.vue"/>
+    <s v="Script d'integration"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="stock-api.js"/>
+    <s v="Fonction filtre selon date et mouvement"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion de stock"/>
+    <s v="ProductDetail.vue"/>
+    <s v="Ajout champ information stock disponible"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion de stock"/>
+    <s v="stock-api.js"/>
+    <s v="Fonction de get de stock disponible"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion de stock"/>
+    <s v="ProductDetail.vue"/>
+    <s v="Get et Affichage de stock dispo"/>
+    <s v="Integration"/>
     <x v="0"/>
     <n v="100"/>
     <n v="100"/>
@@ -1975,34 +2190,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2015,49 +2230,49 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="46.28515625" customWidth="1"/>
+    <col min="5" max="5" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75">
@@ -2065,28 +2280,29 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>38</v>
+      <c r="G2" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H2" s="6">
-        <v>100</v>
-      </c>
-      <c r="I2" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I2" s="6">
+        <f>H2</f>
+        <v>10</v>
       </c>
       <c r="J2" s="8">
         <f t="shared" ref="J2:J4" si="0">H2-I2</f>
@@ -2102,35 +2318,36 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>66</v>
+      <c r="D3" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H3" s="6">
-        <v>100</v>
-      </c>
-      <c r="I3" s="8">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I66" si="1">H3</f>
+        <v>5</v>
       </c>
       <c r="J3" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K3" s="9">
-        <f t="shared" ref="K3:K4" si="1">(I3/(I3+J3))</f>
+        <f t="shared" ref="K3:K4" si="2">(I3/(I3+J3))</f>
         <v>1</v>
       </c>
     </row>
@@ -2139,35 +2356,36 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>128</v>
+      <c r="D4" s="29" t="s">
+        <v>124</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H4" s="6">
-        <v>100</v>
-      </c>
-      <c r="I4" s="8">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="J4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2176,28 +2394,29 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>65</v>
+      <c r="D5" s="29" t="s">
+        <v>64</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H5" s="6">
-        <v>100</v>
-      </c>
-      <c r="I5" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J5" s="8">
         <f>H5-I5</f>
@@ -2213,35 +2432,36 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H6" s="6">
-        <v>100</v>
-      </c>
-      <c r="I6" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" ref="J6:J14" si="2">H6-I6</f>
+        <f t="shared" ref="J6:J14" si="3">H6-I6</f>
         <v>0</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" ref="K6:K48" si="3">(I6/(I6+J6))</f>
+        <f t="shared" ref="K6:K48" si="4">(I6/(I6+J6))</f>
         <v>1</v>
       </c>
     </row>
@@ -2250,35 +2470,36 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H7" s="6">
-        <v>100</v>
-      </c>
-      <c r="I7" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -2287,35 +2508,36 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>67</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H8" s="6">
-        <v>100</v>
-      </c>
-      <c r="I8" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" ref="J8:J10" si="4">H8-I8</f>
+        <f t="shared" ref="J8:J10" si="5">H8-I8</f>
         <v>0</v>
       </c>
       <c r="K8" s="9">
-        <f t="shared" ref="K8:K10" si="5">(I8/(I8+J8))</f>
+        <f t="shared" ref="K8:K10" si="6">(I8/(I8+J8))</f>
         <v>1</v>
       </c>
     </row>
@@ -2324,35 +2546,36 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H9" s="6">
-        <v>100</v>
-      </c>
-      <c r="I9" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -2361,35 +2584,36 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>78</v>
+        <v>42</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>77</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H10" s="6">
-        <v>100</v>
-      </c>
-      <c r="I10" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K10" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -2398,35 +2622,36 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>69</v>
+        <v>42</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H11" s="6">
-        <v>100</v>
-      </c>
-      <c r="I11" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K11" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -2435,35 +2660,36 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H12" s="6">
-        <v>100</v>
-      </c>
-      <c r="I12" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J12" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -2472,35 +2698,36 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>71</v>
+        <v>42</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>70</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H13" s="6">
-        <v>100</v>
-      </c>
-      <c r="I13" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -2509,35 +2736,36 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H14" s="6">
-        <v>100</v>
-      </c>
-      <c r="I14" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -2546,35 +2774,36 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H15" s="6">
-        <v>100</v>
-      </c>
-      <c r="I15" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" ref="J15:J52" si="6">H15-I15</f>
+        <f t="shared" ref="J15:J52" si="7">H15-I15</f>
         <v>0</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" ref="K15:K23" si="7">(I15/(I15+J15))</f>
+        <f t="shared" ref="K15:K23" si="8">(I15/(I15+J15))</f>
         <v>1</v>
       </c>
     </row>
@@ -2583,35 +2812,36 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H16" s="6">
-        <v>100</v>
-      </c>
-      <c r="I16" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K16" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2620,35 +2850,36 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>72</v>
+        <v>97</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H17" s="6">
-        <v>100</v>
-      </c>
-      <c r="I17" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J17" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2657,35 +2888,36 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>85</v>
+        <v>97</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>82</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H18" s="6">
-        <v>100</v>
-      </c>
-      <c r="I18" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2694,35 +2926,36 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>73</v>
+        <v>98</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H19" s="6">
-        <v>100</v>
-      </c>
-      <c r="I19" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2731,35 +2964,36 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>73</v>
+        <v>98</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H20" s="6">
-        <v>100</v>
-      </c>
-      <c r="I20" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2768,35 +3002,36 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>73</v>
+        <v>98</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H21" s="6">
-        <v>100</v>
-      </c>
-      <c r="I21" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2805,35 +3040,36 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>73</v>
+        <v>98</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H22" s="6">
-        <v>100</v>
-      </c>
-      <c r="I22" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2842,35 +3078,36 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>87</v>
+        <v>98</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>84</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H23" s="6">
-        <v>100</v>
-      </c>
-      <c r="I23" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -2879,31 +3116,32 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>88</v>
+        <v>99</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>85</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H24" s="6">
-        <v>100</v>
-      </c>
-      <c r="I24" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K24" s="9">
@@ -2916,31 +3154,32 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>88</v>
+        <v>99</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>85</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H25" s="6">
-        <v>100</v>
-      </c>
-      <c r="I25" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K25" s="9">
@@ -2953,31 +3192,32 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>88</v>
+        <v>99</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>85</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H26" s="6">
-        <v>100</v>
-      </c>
-      <c r="I26" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K26" s="9">
@@ -2990,35 +3230,36 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H27" s="6">
-        <v>100</v>
-      </c>
-      <c r="I27" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" ref="K27:K31" si="8">(I27/(I27+J27))</f>
+        <f t="shared" ref="K27:K31" si="9">(I27/(I27+J27))</f>
         <v>1</v>
       </c>
     </row>
@@ -3027,35 +3268,36 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H28" s="6">
-        <v>100</v>
-      </c>
-      <c r="I28" s="8">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -3064,35 +3306,36 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H29" s="6">
-        <v>100</v>
-      </c>
-      <c r="I29" s="8">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -3101,35 +3344,36 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H30" s="6">
-        <v>100</v>
-      </c>
-      <c r="I30" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -3138,35 +3382,36 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>91</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G31" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H31" s="6">
-        <v>100</v>
-      </c>
-      <c r="I31" s="8">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -3175,35 +3420,36 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="F32" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H32" s="6">
-        <v>100</v>
-      </c>
-      <c r="I32" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" ref="K32" si="9">(I32/(I32+J32))</f>
+        <f t="shared" ref="K32" si="10">(I32/(I32+J32))</f>
         <v>1</v>
       </c>
     </row>
@@ -3212,35 +3458,36 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>102</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H33" s="6">
-        <v>100</v>
-      </c>
-      <c r="I33" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" ref="K33" si="10">(I33/(I33+J33))</f>
+        <f t="shared" ref="K33" si="11">(I33/(I33+J33))</f>
         <v>1</v>
       </c>
     </row>
@@ -3249,35 +3496,36 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>75</v>
+        <v>45</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H34" s="6">
-        <v>100</v>
-      </c>
-      <c r="I34" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J34" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3286,35 +3534,36 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>75</v>
+        <v>45</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H35" s="6">
-        <v>100</v>
-      </c>
-      <c r="I35" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3323,35 +3572,36 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="F36" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H36" s="6">
-        <v>100</v>
-      </c>
-      <c r="I36" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I36" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J36" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3360,35 +3610,36 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>129</v>
+        <v>46</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H37" s="6">
-        <v>100</v>
-      </c>
-      <c r="I37" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I37" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J37" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3397,35 +3648,36 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="31" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>50</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H38" s="6">
-        <v>100</v>
-      </c>
-      <c r="I38" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I38" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J38" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3434,35 +3686,36 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="31" t="s">
-        <v>77</v>
+        <v>55</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H39" s="6">
-        <v>100</v>
-      </c>
-      <c r="I39" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I39" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K39" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3471,35 +3724,36 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="31" t="s">
-        <v>38</v>
+      <c r="G40" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H40" s="6">
-        <v>100</v>
-      </c>
-      <c r="I40" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I40" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J40" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K40" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3508,35 +3762,36 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="31" t="s">
-        <v>77</v>
+        <v>55</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H41" s="6">
-        <v>100</v>
-      </c>
-      <c r="I41" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I41" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J41" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3545,35 +3800,36 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>76</v>
+        <v>55</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>75</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G42" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H42" s="6">
-        <v>100</v>
-      </c>
-      <c r="I42" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I42" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J42" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3582,35 +3838,36 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>129</v>
+        <v>55</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H43" s="6">
-        <v>100</v>
-      </c>
-      <c r="I43" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I43" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J43" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K43" s="9">
-        <f t="shared" ref="K43:K45" si="11">(I43/(I43+J43))</f>
+        <f t="shared" ref="K43:K45" si="12">(I43/(I43+J43))</f>
         <v>1</v>
       </c>
     </row>
@@ -3619,35 +3876,36 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>129</v>
+        <v>55</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H44" s="6">
-        <v>100</v>
-      </c>
-      <c r="I44" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I44" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J44" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K44" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -3656,35 +3914,36 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="31" t="s">
-        <v>129</v>
+        <v>55</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H45" s="6">
-        <v>100</v>
-      </c>
-      <c r="I45" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I45" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J45" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K45" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -3693,35 +3952,36 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="F46" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H46" s="6">
-        <v>100</v>
-      </c>
-      <c r="I46" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I46" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J46" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K46" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3730,35 +3990,36 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>76</v>
+        <v>55</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>75</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H47" s="6">
-        <v>100</v>
-      </c>
-      <c r="I47" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I47" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J47" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K47" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3767,35 +4028,36 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>84</v>
+        <v>80</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H48" s="6">
-        <v>100</v>
-      </c>
-      <c r="I48" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I48" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J48" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K48" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -3804,35 +4066,36 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>129</v>
+        <v>80</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H49" s="6">
-        <v>100</v>
-      </c>
-      <c r="I49" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I49" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J49" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K49" s="9">
-        <f t="shared" ref="K49:K52" si="12">(I49/(I49+J49))</f>
+        <f t="shared" ref="K49:K52" si="13">(I49/(I49+J49))</f>
         <v>1</v>
       </c>
     </row>
@@ -3841,35 +4104,36 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>129</v>
+        <v>80</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H50" s="6">
-        <v>100</v>
-      </c>
-      <c r="I50" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I50" s="6">
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J50" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K50" s="9">
-        <f t="shared" ref="K50:K51" si="13">(I50/(I50+J50))</f>
+        <f t="shared" ref="K50:K51" si="14">(I50/(I50+J50))</f>
         <v>1</v>
       </c>
     </row>
@@ -3878,35 +4142,36 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51" s="31" t="s">
-        <v>129</v>
+        <v>106</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H51" s="6">
-        <v>100</v>
-      </c>
-      <c r="I51" s="8">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="I51" s="6">
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K51" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -3915,35 +4180,36 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52" s="31" t="s">
-        <v>84</v>
+        <v>106</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G52" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H52" s="6">
-        <v>100</v>
-      </c>
-      <c r="I52" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I52" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K52" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -3952,35 +4218,36 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="31" t="s">
-        <v>110</v>
+        <v>46</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>107</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G53" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H53" s="6">
-        <v>100</v>
-      </c>
-      <c r="I53" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I53" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J53" s="8">
-        <f t="shared" ref="J53" si="14">H53-I53</f>
+        <f t="shared" ref="J53" si="15">H53-I53</f>
         <v>0</v>
       </c>
       <c r="K53" s="9">
-        <f t="shared" ref="K53" si="15">(I53/(I53+J53))</f>
+        <f t="shared" ref="K53" si="16">(I53/(I53+J53))</f>
         <v>1</v>
       </c>
     </row>
@@ -3989,35 +4256,36 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>110</v>
+        <v>46</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>107</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G54" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G54" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H54" s="6">
-        <v>100</v>
-      </c>
-      <c r="I54" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I54" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="J54" s="8">
-        <f t="shared" ref="J54:J55" si="16">H54-I54</f>
+        <f t="shared" ref="J54:J55" si="17">H54-I54</f>
         <v>0</v>
       </c>
       <c r="K54" s="9">
-        <f t="shared" ref="K54" si="17">(I54/(I54+J54))</f>
+        <f t="shared" ref="K54" si="18">(I54/(I54+J54))</f>
         <v>1</v>
       </c>
     </row>
@@ -4026,31 +4294,32 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>110</v>
+        <v>17</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>107</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G55" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H55" s="6">
-        <v>100</v>
-      </c>
-      <c r="I55" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I55" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J55" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K55" s="9">
@@ -4063,35 +4332,36 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>110</v>
+        <v>17</v>
+      </c>
+      <c r="C56" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>107</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H56" s="6">
-        <v>100</v>
-      </c>
-      <c r="I56" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I56" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J56" s="8">
-        <f t="shared" ref="J56:J61" si="18">H56-I56</f>
+        <f t="shared" ref="J56:J61" si="19">H56-I56</f>
         <v>0</v>
       </c>
       <c r="K56" s="9">
-        <f t="shared" ref="K56:K61" si="19">(I56/(I56+J56))</f>
+        <f t="shared" ref="K56:K61" si="20">(I56/(I56+J56))</f>
         <v>1</v>
       </c>
     </row>
@@ -4100,35 +4370,36 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" s="31" t="s">
-        <v>129</v>
+        <v>17</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H57" s="6">
-        <v>100</v>
-      </c>
-      <c r="I57" s="8">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="I57" s="6">
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="J57" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K57" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -4137,35 +4408,36 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>77</v>
+        <v>17</v>
+      </c>
+      <c r="C58" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G58" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H58" s="6">
-        <v>100</v>
-      </c>
-      <c r="I58" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K58" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -4174,35 +4446,36 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="31" t="s">
-        <v>129</v>
+        <v>17</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H59" s="6">
-        <v>100</v>
-      </c>
-      <c r="I59" s="8">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I59" s="6">
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="J59" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K59" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -4211,35 +4484,36 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" s="31" t="s">
-        <v>77</v>
+        <v>17</v>
+      </c>
+      <c r="C60" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G60" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H60" s="6">
-        <v>100</v>
-      </c>
-      <c r="I60" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I60" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J60" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K60" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -4248,35 +4522,36 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D61" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="F61" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H61" s="6">
-        <v>100</v>
-      </c>
-      <c r="I61" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I61" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J61" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K61" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -4285,35 +4560,36 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>68</v>
+        <v>113</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>67</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G62" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H62" s="6">
-        <v>100</v>
-      </c>
-      <c r="I62" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I62" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J62" s="8">
-        <f t="shared" ref="J62" si="20">H62-I62</f>
+        <f t="shared" ref="J62" si="21">H62-I62</f>
         <v>0</v>
       </c>
       <c r="K62" s="9">
-        <f t="shared" ref="K62" si="21">(I62/(I62+J62))</f>
+        <f t="shared" ref="K62" si="22">(I62/(I62+J62))</f>
         <v>1</v>
       </c>
     </row>
@@ -4322,35 +4598,36 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D63" s="31" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>115</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G63" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H63" s="6">
-        <v>100</v>
-      </c>
-      <c r="I63" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I63" s="6">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J63" s="8">
-        <f t="shared" ref="J63" si="22">H63-I63</f>
+        <f t="shared" ref="J63" si="23">H63-I63</f>
         <v>0</v>
       </c>
       <c r="K63" s="9">
-        <f t="shared" ref="K63" si="23">(I63/(I63+J63))</f>
+        <f t="shared" ref="K63" si="24">(I63/(I63+J63))</f>
         <v>1</v>
       </c>
     </row>
@@ -4359,35 +4636,36 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C64" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D64" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="F64" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H64" s="6">
-        <v>100</v>
-      </c>
-      <c r="I64" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I64" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J64" s="8">
-        <f t="shared" ref="J64:J66" si="24">H64-I64</f>
+        <f t="shared" ref="J64:J66" si="25">H64-I64</f>
         <v>0</v>
       </c>
       <c r="K64" s="9">
-        <f t="shared" ref="K64:K66" si="25">(I64/(I64+J64))</f>
+        <f t="shared" ref="K64:K66" si="26">(I64/(I64+J64))</f>
         <v>1</v>
       </c>
     </row>
@@ -4396,35 +4674,36 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D65" s="31" t="s">
-        <v>128</v>
+        <v>114</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>124</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G65" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H65" s="6">
-        <v>100</v>
-      </c>
-      <c r="I65" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I65" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J65" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K65" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
     </row>
@@ -4433,35 +4712,36 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" s="31" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>115</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G66" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H66" s="6">
-        <v>100</v>
-      </c>
-      <c r="I66" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I66" s="6">
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J66" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K66" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
     </row>
@@ -4470,35 +4750,36 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D67" s="31" t="s">
-        <v>77</v>
+        <v>119</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H67" s="6">
-        <v>100</v>
-      </c>
-      <c r="I67" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I67" s="6">
+        <f t="shared" ref="I67:I93" si="27">H67</f>
+        <v>15</v>
       </c>
       <c r="J67" s="8">
-        <f t="shared" ref="J67" si="26">H67-I67</f>
+        <f t="shared" ref="J67" si="28">H67-I67</f>
         <v>0</v>
       </c>
       <c r="K67" s="9">
-        <f t="shared" ref="K67" si="27">(I67/(I67+J67))</f>
+        <f t="shared" ref="K67" si="29">(I67/(I67+J67))</f>
         <v>1</v>
       </c>
     </row>
@@ -4507,35 +4788,36 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D68" s="31" t="s">
-        <v>129</v>
+        <v>119</v>
+      </c>
+      <c r="D68" s="29" t="s">
+        <v>125</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G68" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H68" s="6">
-        <v>100</v>
-      </c>
-      <c r="I68" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I68" s="6">
+        <f t="shared" si="27"/>
+        <v>10</v>
       </c>
       <c r="J68" s="8">
-        <f t="shared" ref="J68:J71" si="28">H68-I68</f>
+        <f t="shared" ref="J68:J71" si="30">H68-I68</f>
         <v>0</v>
       </c>
       <c r="K68" s="9">
-        <f t="shared" ref="K68:K71" si="29">(I68/(I68+J68))</f>
+        <f t="shared" ref="K68:K71" si="31">(I68/(I68+J68))</f>
         <v>1</v>
       </c>
     </row>
@@ -4544,35 +4826,36 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D69" s="31" t="s">
-        <v>77</v>
+        <v>119</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G69" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H69" s="6">
-        <v>100</v>
-      </c>
-      <c r="I69" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I69" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
       </c>
       <c r="J69" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K69" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
     </row>
@@ -4581,35 +4864,36 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D70" s="31" t="s">
-        <v>77</v>
+        <v>119</v>
+      </c>
+      <c r="D70" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G70" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H70" s="6">
-        <v>100</v>
-      </c>
-      <c r="I70" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I70" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
       </c>
       <c r="J70" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K70" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
     </row>
@@ -4618,35 +4902,36 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D71" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="F71" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G71" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H71" s="6">
-        <v>100</v>
-      </c>
-      <c r="I71" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I71" s="6">
+        <f t="shared" si="27"/>
+        <v>20</v>
       </c>
       <c r="J71" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K71" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
     </row>
@@ -4655,35 +4940,36 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" s="31" t="s">
-        <v>85</v>
+        <v>97</v>
+      </c>
+      <c r="D72" s="29" t="s">
+        <v>82</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G72" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H72" s="6">
-        <v>100</v>
-      </c>
-      <c r="I72" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I72" s="6">
+        <f t="shared" si="27"/>
+        <v>10</v>
       </c>
       <c r="J72" s="8">
-        <f t="shared" ref="J72" si="30">H72-I72</f>
+        <f t="shared" ref="J72" si="32">H72-I72</f>
         <v>0</v>
       </c>
       <c r="K72" s="9">
-        <f t="shared" ref="K72" si="31">(I72/(I72+J72))</f>
+        <f t="shared" ref="K72" si="33">(I72/(I72+J72))</f>
         <v>1</v>
       </c>
     </row>
@@ -4692,35 +4978,36 @@
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D73" s="31" t="s">
-        <v>87</v>
+        <v>98</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>84</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G73" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H73" s="6">
-        <v>100</v>
-      </c>
-      <c r="I73" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I73" s="6">
+        <f t="shared" si="27"/>
+        <v>10</v>
       </c>
       <c r="J73" s="8">
-        <f t="shared" ref="J73:J74" si="32">H73-I73</f>
+        <f t="shared" ref="J73:J74" si="34">H73-I73</f>
         <v>0</v>
       </c>
       <c r="K73" s="9">
-        <f t="shared" ref="K73:K74" si="33">(I73/(I73+J73))</f>
+        <f t="shared" ref="K73:K74" si="35">(I73/(I73+J73))</f>
         <v>1</v>
       </c>
     </row>
@@ -4729,35 +5016,36 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D74" s="31" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="D74" s="29" t="s">
+        <v>91</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G74" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G74" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H74" s="6">
-        <v>100</v>
-      </c>
-      <c r="I74" s="8">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="I74" s="6">
+        <f t="shared" si="27"/>
+        <v>10</v>
       </c>
       <c r="J74" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K74" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
     </row>
@@ -4766,35 +5054,36 @@
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D75" s="31" t="s">
-        <v>75</v>
+        <v>45</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G75" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H75" s="6">
-        <v>100</v>
-      </c>
-      <c r="I75" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I75" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
       </c>
       <c r="J75" s="8">
-        <f t="shared" ref="J75" si="34">H75-I75</f>
+        <f t="shared" ref="J75" si="36">H75-I75</f>
         <v>0</v>
       </c>
       <c r="K75" s="9">
-        <f t="shared" ref="K75" si="35">(I75/(I75+J75))</f>
+        <f t="shared" ref="K75" si="37">(I75/(I75+J75))</f>
         <v>1</v>
       </c>
     </row>
@@ -4803,35 +5092,36 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D76" s="31" t="s">
-        <v>133</v>
+        <v>146</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>147</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G76" s="31" t="s">
-        <v>38</v>
+        <v>148</v>
+      </c>
+      <c r="G76" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H76" s="6">
-        <v>100</v>
-      </c>
-      <c r="I76" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I76" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
       </c>
       <c r="J76" s="8">
-        <f t="shared" ref="J76:J80" si="36">H76-I76</f>
+        <f t="shared" ref="J76" si="38">H76-I76</f>
         <v>0</v>
       </c>
       <c r="K76" s="9">
-        <f t="shared" ref="K76:K80" si="37">(I76/(I76+J76))</f>
+        <f t="shared" ref="K76" si="39">(I76/(I76+J76))</f>
         <v>1</v>
       </c>
     </row>
@@ -4840,35 +5130,36 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D77" s="31" t="s">
-        <v>134</v>
+        <v>146</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>67</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G77" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G77" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H77" s="6">
-        <v>100</v>
-      </c>
-      <c r="I77" s="8">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I77" s="6">
+        <f t="shared" si="27"/>
+        <v>25</v>
       </c>
       <c r="J77" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="J77:J80" si="40">H77-I77</f>
         <v>0</v>
       </c>
       <c r="K77" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="K77:K80" si="41">(I77/(I77+J77))</f>
         <v>1</v>
       </c>
     </row>
@@ -4877,35 +5168,36 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D78" s="31" t="s">
-        <v>133</v>
+        <v>146</v>
+      </c>
+      <c r="D78" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G78" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G78" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H78" s="6">
-        <v>100</v>
-      </c>
-      <c r="I78" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I78" s="6">
+        <f t="shared" si="27"/>
+        <v>30</v>
       </c>
       <c r="J78" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K78" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
     </row>
@@ -4914,35 +5206,36 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D79" s="31" t="s">
-        <v>133</v>
+        <v>146</v>
+      </c>
+      <c r="D79" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H79" s="6">
-        <v>100</v>
-      </c>
-      <c r="I79" s="8">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I79" s="6">
+        <f t="shared" si="27"/>
+        <v>40</v>
       </c>
       <c r="J79" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K79" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
     </row>
@@ -4951,35 +5244,36 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D80" s="31" t="s">
-        <v>134</v>
+        <v>146</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G80" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G80" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H80" s="6">
-        <v>100</v>
-      </c>
-      <c r="I80" s="8">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="I80" s="6">
+        <f t="shared" si="27"/>
+        <v>45</v>
       </c>
       <c r="J80" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K80" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
     </row>
@@ -4988,35 +5282,36 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D81" s="31" t="s">
-        <v>133</v>
+        <v>146</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G81" s="31" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="G81" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H81" s="6">
-        <v>100</v>
-      </c>
-      <c r="I81" s="8">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="I81" s="6">
+        <f t="shared" si="27"/>
+        <v>30</v>
       </c>
       <c r="J81" s="8">
-        <f t="shared" ref="J81:J82" si="38">H81-I81</f>
+        <f t="shared" ref="J81" si="42">H81-I81</f>
         <v>0</v>
       </c>
       <c r="K81" s="9">
-        <f t="shared" ref="K81:K82" si="39">(I81/(I81+J81))</f>
+        <f t="shared" ref="K81" si="43">(I81/(I81+J81))</f>
         <v>1</v>
       </c>
     </row>
@@ -5025,35 +5320,36 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D82" s="31" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>129</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G82" s="31" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="G82" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H82" s="6">
-        <v>100</v>
-      </c>
-      <c r="I82" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I82" s="6">
+        <f t="shared" si="27"/>
+        <v>20</v>
       </c>
       <c r="J82" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="J82:J86" si="44">H82-I82</f>
         <v>0</v>
       </c>
       <c r="K82" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="K82:K86" si="45">(I82/(I82+J82))</f>
         <v>1</v>
       </c>
     </row>
@@ -5062,35 +5358,36 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D83" s="31" t="s">
-        <v>76</v>
+        <v>128</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>133</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G83" s="31" t="s">
-        <v>38</v>
+      <c r="G83" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H83" s="6">
-        <v>100</v>
-      </c>
-      <c r="I83" s="8">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I83" s="6">
+        <f t="shared" si="27"/>
+        <v>20</v>
       </c>
       <c r="J83" s="8">
-        <f t="shared" ref="J83" si="40">H83-I83</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K83" s="9">
-        <f t="shared" ref="K83" si="41">(I83/(I83+J83))</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
     </row>
@@ -5099,35 +5396,36 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D84" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" s="29" t="s">
         <v>134</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G84" s="31" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="G84" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="H84" s="6">
-        <v>100</v>
-      </c>
-      <c r="I84" s="8">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="I84" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
       </c>
       <c r="J84" s="8">
-        <f t="shared" ref="J84:J85" si="42">H84-I84</f>
+        <f t="shared" ref="J84" si="46">H84-I84</f>
         <v>0</v>
       </c>
       <c r="K84" s="9">
-        <f t="shared" ref="K84:K85" si="43">(I84/(I84+J84))</f>
+        <f t="shared" ref="K84" si="47">(I84/(I84+J84))</f>
         <v>1</v>
       </c>
     </row>
@@ -5136,40 +5434,345 @@
         <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D85" s="31" t="s">
-        <v>76</v>
+        <v>128</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>143</v>
       </c>
       <c r="E85" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H85" s="6">
+        <v>2</v>
+      </c>
+      <c r="I85" s="6">
+        <f t="shared" si="27"/>
+        <v>2</v>
+      </c>
+      <c r="J85" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="9">
+        <f t="shared" si="45"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="12.75">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H86" s="6">
+        <v>15</v>
+      </c>
+      <c r="I86" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
+      </c>
+      <c r="J86" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="9">
+        <f t="shared" si="45"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="12.75">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H87" s="6">
+        <v>15</v>
+      </c>
+      <c r="I87" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
+      </c>
+      <c r="J87" s="8">
+        <f t="shared" ref="J87:J88" si="48">H87-I87</f>
+        <v>0</v>
+      </c>
+      <c r="K87" s="9">
+        <f t="shared" ref="K87:K88" si="49">(I87/(I87+J87))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="12.75">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D88" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E88" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G85" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="H85" s="6">
-        <v>100</v>
-      </c>
-      <c r="I85" s="8">
-        <v>100</v>
-      </c>
-      <c r="J85" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="9">
-        <f t="shared" si="43"/>
+      <c r="F88" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H88" s="6">
+        <v>30</v>
+      </c>
+      <c r="I88" s="6">
+        <f t="shared" si="27"/>
+        <v>30</v>
+      </c>
+      <c r="J88" s="8">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="9">
+        <f t="shared" si="49"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="12.75">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H89" s="6">
+        <v>30</v>
+      </c>
+      <c r="I89" s="6">
+        <f t="shared" si="27"/>
+        <v>30</v>
+      </c>
+      <c r="J89" s="8">
+        <f t="shared" ref="J89" si="50">H89-I89</f>
+        <v>0</v>
+      </c>
+      <c r="K89" s="9">
+        <f t="shared" ref="K89" si="51">(I89/(I89+J89))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="12.75">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D90" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H90" s="6">
+        <v>20</v>
+      </c>
+      <c r="I90" s="6">
+        <f t="shared" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="J90" s="8">
+        <f t="shared" ref="J90" si="52">H90-I90</f>
+        <v>0</v>
+      </c>
+      <c r="K90" s="9">
+        <f t="shared" ref="K90" si="53">(I90/(I90+J90))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="12.75">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D91" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H91" s="6">
+        <v>30</v>
+      </c>
+      <c r="I91" s="6">
+        <f t="shared" si="27"/>
+        <v>30</v>
+      </c>
+      <c r="J91" s="8">
+        <f t="shared" ref="J91" si="54">H91-I91</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="9">
+        <f t="shared" ref="K91" si="55">(I91/(I91+J91))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="12.75">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D92" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H92" s="6">
+        <v>5</v>
+      </c>
+      <c r="I92" s="6">
+        <f t="shared" si="27"/>
+        <v>5</v>
+      </c>
+      <c r="J92" s="8">
+        <f t="shared" ref="J92" si="56">H92-I92</f>
+        <v>0</v>
+      </c>
+      <c r="K92" s="9">
+        <f t="shared" ref="K92" si="57">(I92/(I92+J92))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="12.75">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D93" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H93" s="6">
+        <v>15</v>
+      </c>
+      <c r="I93" s="6">
+        <f t="shared" si="27"/>
+        <v>15</v>
+      </c>
+      <c r="J93" s="8">
+        <f>H93-I93</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="9">
+        <f>(I93/(I93+J93))</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5181,72 +5784,77 @@
   </sheetPr>
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
-      <c r="A1" s="23"/>
-      <c r="B1" s="24" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:4" ht="12.75">
+      <c r="A2" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4" ht="12.75">
-      <c r="A2" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="D2" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="28" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="12.75">
+      <c r="A3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="30">
+        <v>8400</v>
+      </c>
+      <c r="C3" s="31">
+        <v>8400</v>
+      </c>
+      <c r="D3" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12.75">
+      <c r="A4" s="27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="12.75">
-      <c r="A3" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="32">
-        <v>7000</v>
-      </c>
-      <c r="C3" s="33">
-        <v>7000</v>
-      </c>
-      <c r="D3" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="12.75">
-      <c r="A4" s="29" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
+    </row>
+    <row r="5" spans="1:4" ht="12.75">
+      <c r="A5" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37"/>
-    </row>
-    <row r="5" spans="1:4" ht="12.75">
-      <c r="A5" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="38">
-        <v>7000</v>
-      </c>
-      <c r="C5" s="39">
-        <v>7000</v>
-      </c>
-      <c r="D5" s="40">
+      <c r="B5" s="36">
+        <v>8400</v>
+      </c>
+      <c r="C5" s="37">
+        <v>8400</v>
+      </c>
+      <c r="D5" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75"/>
     <row r="7" spans="1:4" ht="12.75"/>
     <row r="12" spans="1:4" ht="12.75">
-      <c r="A12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="A12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11">
         <f>avancement!D2</f>
         <v>1</v>
       </c>
@@ -5272,55 +5880,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="13" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="13">
+        <f>SUM('liste des taches'!H:H)</f>
+        <v>1917</v>
+      </c>
+      <c r="B2" s="13">
+        <f>SUM('liste des taches'!I:I)</f>
+        <v>1917</v>
+      </c>
+      <c r="C2" s="13">
+        <f>SUM('liste des taches'!J:J)</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="14">
+        <f>(B2/(B2+C2))</f>
+        <v>1</v>
+      </c>
+      <c r="E2" s="15">
+        <f>((B2+C2)-A2)/A2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="13">
+        <f>C2/60</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="14">
-        <f>SUM('liste des taches'!H:H)</f>
-        <v>8400</v>
-      </c>
-      <c r="B2" s="14">
-        <f>SUM('liste des taches'!I:I)</f>
-        <v>8400</v>
-      </c>
-      <c r="C2" s="14">
-        <f>SUM('liste des taches'!J:J)</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="15">
-        <f>(B2/(B2+C2))</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="16">
-        <f>((B2+C2)-A2)/A2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="14">
-        <f>C2/60</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5332,139 +5940,1246 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A1" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="20">
-        <v>46048</v>
-      </c>
-      <c r="D1" s="20">
-        <v>46049</v>
-      </c>
-      <c r="E1" s="20">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="21">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14">
-        <f t="shared" ref="B2:B10" si="0">SUM(D2:P2)</f>
-        <v>20</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="21">
-        <v>20</v>
-      </c>
-      <c r="E2" s="17"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="21">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="19">
+        <v>46153</v>
+      </c>
+      <c r="D1" s="19">
+        <v>46154</v>
+      </c>
+      <c r="E1" s="19">
+        <v>46155</v>
+      </c>
+      <c r="F1" s="19">
+        <v>46156</v>
+      </c>
+      <c r="G1" s="19">
+        <v>46157</v>
+      </c>
+      <c r="H1" s="19">
+        <v>46158</v>
+      </c>
+      <c r="I1" s="19">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13">
+        <f>SUM(C2:P2)</f>
+        <v>10</v>
+      </c>
+      <c r="C2" s="16">
+        <f>'liste des taches'!H2</f>
+        <v>10</v>
+      </c>
+      <c r="D2" s="20"/>
+      <c r="E2" s="16"/>
+      <c r="K2" s="39"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
+        <f t="shared" ref="B3:B66" si="0">SUM(C3:P3)</f>
+        <v>5</v>
+      </c>
+      <c r="C3" s="16">
+        <f>'liste des taches'!H3</f>
+        <v>5</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A4" s="20">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A4" s="21">
-        <v>3</v>
-      </c>
-      <c r="B4" s="14">
+        <v>5</v>
+      </c>
+      <c r="C4" s="16">
+        <f>'liste des taches'!H4</f>
+        <v>5</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A5" s="20">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C4" s="21">
-        <v>20</v>
-      </c>
-      <c r="D4" s="21">
+      <c r="C5" s="16">
+        <f>'liste des taches'!H5</f>
         <v>10</v>
       </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A5" s="21">
-        <v>4</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="D5" s="20"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A6" s="20">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A6" s="21">
-        <v>5</v>
-      </c>
-      <c r="B6" s="14">
+        <v>15</v>
+      </c>
+      <c r="C6" s="16">
+        <f>'liste des taches'!H6</f>
+        <v>15</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A7" s="20">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="22">
+      <c r="C7" s="16">
+        <f>'liste des taches'!H7</f>
         <v>10</v>
       </c>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A7" s="21">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="D7" s="20"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A8" s="20">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A8" s="21">
-        <v>7</v>
-      </c>
-      <c r="B8" s="14">
+        <v>15</v>
+      </c>
+      <c r="C8" s="16">
+        <f>'liste des taches'!H8</f>
+        <v>15</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A9" s="20">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13">
         <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="22">
-        <v>90</v>
-      </c>
-      <c r="E8" s="17"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14">
+        <v>15</v>
+      </c>
+      <c r="C9" s="16">
+        <f>'liste des taches'!H9</f>
+        <v>15</v>
+      </c>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C10" s="16">
+        <f>'liste des taches'!H10</f>
+        <v>10</v>
+      </c>
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A11" s="20">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C11" s="16">
+        <f>'liste des taches'!H11</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A12" s="20">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C12" s="16">
+        <f>'liste des taches'!H12</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A13" s="20">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C13" s="16">
+        <f>'liste des taches'!H13</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A14" s="20">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14">
+        <f>'liste des taches'!H14</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A15" s="20">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15">
+        <f>'liste des taches'!H15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A16" s="20">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16">
+        <f>'liste des taches'!H16</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A17" s="20">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17">
+        <f>'liste des taches'!H17</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A18" s="20">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <f>'liste des taches'!H18</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A19" s="20">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D19">
+        <f>'liste des taches'!H19</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A20" s="20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D20">
+        <f>'liste des taches'!H20</f>
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A21" s="20">
+        <v>20</v>
+      </c>
+      <c r="B21" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <f>'liste des taches'!H21</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A22" s="20">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <f>'liste des taches'!H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A23" s="20">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D23">
+        <f>'liste des taches'!H23</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A24" s="20">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <f>'liste des taches'!H24</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A25" s="20">
+        <v>24</v>
+      </c>
+      <c r="B25" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <f>'liste des taches'!H25</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A26" s="20">
+        <v>25</v>
+      </c>
+      <c r="B26" s="13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <f>'liste des taches'!H26</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A27" s="20">
+        <v>26</v>
+      </c>
+      <c r="B27" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D27">
+        <f>'liste des taches'!H27</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A28" s="20">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="D28">
+        <f>'liste des taches'!H28</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A29" s="20">
+        <v>28</v>
+      </c>
+      <c r="B29" s="13">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <f>'liste des taches'!H29</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A30" s="20">
+        <v>29</v>
+      </c>
+      <c r="B30" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <f>'liste des taches'!H30</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A31" s="20">
+        <v>30</v>
+      </c>
+      <c r="B31" s="13">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="D31">
+        <f>'liste des taches'!H31</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A32" s="20">
+        <v>31</v>
+      </c>
+      <c r="B32" s="13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <f>'liste des taches'!H32</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A33" s="20">
+        <v>32</v>
+      </c>
+      <c r="B33" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <f>'liste des taches'!H33</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A34" s="20">
+        <v>33</v>
+      </c>
+      <c r="B34" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <f>'liste des taches'!H34</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A35" s="20">
+        <v>34</v>
+      </c>
+      <c r="B35" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D35">
+        <f>'liste des taches'!H35</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A36" s="20">
+        <v>35</v>
+      </c>
+      <c r="B36" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D36">
+        <f>'liste des taches'!H36</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A37" s="20">
+        <v>36</v>
+      </c>
+      <c r="B37" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <f>'liste des taches'!H37</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A38" s="20">
+        <v>37</v>
+      </c>
+      <c r="B38" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <f>'liste des taches'!H38</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A39" s="20">
+        <v>38</v>
+      </c>
+      <c r="B39" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E39">
+        <f>'liste des taches'!H39</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A40" s="20">
+        <v>39</v>
+      </c>
+      <c r="B40" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E40">
+        <f>'liste des taches'!H40</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A41" s="20">
+        <v>40</v>
+      </c>
+      <c r="B41" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E41">
+        <f>'liste des taches'!H41</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A42" s="20">
+        <v>41</v>
+      </c>
+      <c r="B42" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E42">
+        <f>'liste des taches'!H42</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A43" s="20">
+        <v>42</v>
+      </c>
+      <c r="B43" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E43">
+        <f>'liste des taches'!H43</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A44" s="20">
+        <v>43</v>
+      </c>
+      <c r="B44" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E44">
+        <f>'liste des taches'!H44</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A45" s="20">
+        <v>44</v>
+      </c>
+      <c r="B45" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E45">
+        <f>'liste des taches'!H45</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A46" s="20">
+        <v>45</v>
+      </c>
+      <c r="B46" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E46">
+        <f>'liste des taches'!H46</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A47" s="20">
+        <v>46</v>
+      </c>
+      <c r="B47" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E47">
+        <f>'liste des taches'!H47</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A48" s="20">
+        <v>47</v>
+      </c>
+      <c r="B48" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F48">
+        <f>'liste des taches'!H48</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A49" s="20">
+        <v>48</v>
+      </c>
+      <c r="B49" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F49">
+        <f>'liste des taches'!H49</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A50" s="20">
+        <v>49</v>
+      </c>
+      <c r="B50" s="13">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F50">
+        <f>'liste des taches'!H50</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A51" s="20">
+        <v>50</v>
+      </c>
+      <c r="B51" s="13">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="F51">
+        <f>'liste des taches'!H51</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A52" s="20">
+        <v>51</v>
+      </c>
+      <c r="B52" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F52">
+        <f>'liste des taches'!H52</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A53" s="20">
+        <v>52</v>
+      </c>
+      <c r="B53" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <f>'liste des taches'!H53</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A54" s="20">
+        <v>53</v>
+      </c>
+      <c r="B54" s="13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <f>'liste des taches'!H54</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A55" s="20">
+        <v>54</v>
+      </c>
+      <c r="B55" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F55">
+        <f>'liste des taches'!H55</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A56" s="20">
+        <v>55</v>
+      </c>
+      <c r="B56" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F56">
+        <f>'liste des taches'!H56</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A57" s="20">
+        <v>56</v>
+      </c>
+      <c r="B57" s="13">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="F57">
+        <f>'liste des taches'!H57</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A58" s="20">
+        <v>57</v>
+      </c>
+      <c r="B58" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F58">
+        <f>'liste des taches'!H58</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A59" s="20">
+        <v>58</v>
+      </c>
+      <c r="B59" s="13">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F59">
+        <f>'liste des taches'!H59</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A60" s="20">
+        <v>59</v>
+      </c>
+      <c r="B60" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F60">
+        <f>'liste des taches'!H60</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A61" s="20">
+        <v>60</v>
+      </c>
+      <c r="B61" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F61">
+        <f>'liste des taches'!H61</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A62" s="20">
+        <v>61</v>
+      </c>
+      <c r="B62" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F62">
+        <f>'liste des taches'!H62</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A63" s="20">
+        <v>62</v>
+      </c>
+      <c r="B63" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <f>'liste des taches'!H63</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A64" s="20">
+        <v>63</v>
+      </c>
+      <c r="B64" s="13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F64">
+        <f>'liste des taches'!H64</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A65" s="20">
+        <v>64</v>
+      </c>
+      <c r="B65" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F65">
+        <f>'liste des taches'!H65</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A66" s="20">
+        <v>65</v>
+      </c>
+      <c r="B66" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F66">
+        <f>'liste des taches'!H66</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A67" s="20">
+        <v>66</v>
+      </c>
+      <c r="B67" s="13">
+        <f t="shared" ref="B67:B92" si="1">SUM(C67:P67)</f>
+        <v>15</v>
+      </c>
+      <c r="F67">
+        <f>'liste des taches'!H67</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A68" s="20">
+        <v>67</v>
+      </c>
+      <c r="B68" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F68">
+        <f>'liste des taches'!H68</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A69" s="20">
+        <v>68</v>
+      </c>
+      <c r="B69" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F69">
+        <f>'liste des taches'!H69</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A70" s="20">
+        <v>69</v>
+      </c>
+      <c r="B70" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F70">
+        <f>'liste des taches'!H70</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A71" s="20">
+        <v>70</v>
+      </c>
+      <c r="B71" s="13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="F71">
+        <f>'liste des taches'!H71</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A72" s="20">
+        <v>71</v>
+      </c>
+      <c r="B72" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G72">
+        <f>'liste des taches'!H72</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A73" s="20">
+        <v>72</v>
+      </c>
+      <c r="B73" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G73">
+        <f>'liste des taches'!H73</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A74" s="20">
+        <v>73</v>
+      </c>
+      <c r="B74" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G74">
+        <f>'liste des taches'!H74</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A75" s="20">
+        <v>74</v>
+      </c>
+      <c r="B75" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="G75">
+        <f>'liste des taches'!H75</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A76" s="20">
+        <v>75</v>
+      </c>
+      <c r="B76" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="G76">
+        <f>'liste des taches'!H76</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A77" s="20">
+        <v>76</v>
+      </c>
+      <c r="B77" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="H77">
+        <f>'liste des taches'!H76</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A78" s="20">
+        <v>77</v>
+      </c>
+      <c r="B78" s="13">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="H78">
+        <f>'liste des taches'!H77</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A79" s="20">
+        <v>78</v>
+      </c>
+      <c r="B79" s="13">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="H79">
+        <f>'liste des taches'!H78</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A80" s="20">
+        <v>79</v>
+      </c>
+      <c r="B80" s="13">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="H80">
+        <f>'liste des taches'!H79</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A81" s="20">
+        <v>80</v>
+      </c>
+      <c r="B81" s="13">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="H81">
+        <f>'liste des taches'!H80</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A82" s="20">
+        <v>81</v>
+      </c>
+      <c r="B82" s="13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I82">
+        <f>'liste des taches'!H82</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A83" s="20">
+        <v>82</v>
+      </c>
+      <c r="B83" s="13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I83">
+        <f>'liste des taches'!H83</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A84" s="20">
+        <v>83</v>
+      </c>
+      <c r="B84" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I84">
+        <f>'liste des taches'!H84</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A85" s="20">
+        <v>84</v>
+      </c>
+      <c r="B85" s="13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I85">
+        <f>'liste des taches'!H85</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A86" s="20">
+        <v>85</v>
+      </c>
+      <c r="B86" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I86">
+        <f>'liste des taches'!H86</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A87" s="20">
+        <v>86</v>
+      </c>
+      <c r="B87" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I87">
+        <f>'liste des taches'!H87</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A88" s="20">
+        <v>87</v>
+      </c>
+      <c r="B88" s="13">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="I88">
+        <f>'liste des taches'!H88</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A89" s="20">
+        <v>88</v>
+      </c>
+      <c r="B89" s="13">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="I89">
+        <f>'liste des taches'!H89</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A90" s="20">
+        <v>89</v>
+      </c>
+      <c r="B90" s="13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I90">
+        <f>'liste des taches'!H90</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A91" s="20">
+        <v>90</v>
+      </c>
+      <c r="B91" s="13">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="I91">
+        <f>'liste des taches'!H91</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A92" s="20">
+        <v>91</v>
+      </c>
+      <c r="B92" s="13">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="I92">
+        <f>'liste des taches'!H92</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15.75" customHeight="1">
+      <c r="I93">
+        <f>'liste des taches'!H93</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Todo Cloud S5.xlsx
+++ b/Todo Cloud S5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EVAL\1_PrestaShop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84541F7B-B3C2-4969-8AD7-AE22D0A69CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405CDB05-BA9E-4FC7-B4A4-375EB51BE326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="170">
   <si>
     <t>A</t>
   </si>
@@ -131,379 +131,412 @@
     <t>SUM of Reste à faire</t>
   </si>
   <si>
+    <t>Creation interface</t>
+  </si>
+  <si>
+    <t>ETU003295</t>
+  </si>
+  <si>
+    <t>script de verification</t>
+  </si>
+  <si>
+    <t>Protections Pages</t>
+  </si>
+  <si>
+    <t>mode FO ou BO</t>
+  </si>
+  <si>
+    <t>Layouts separe FO ouBO</t>
+  </si>
+  <si>
+    <t>Gestion Donne</t>
+  </si>
+  <si>
+    <t>fonctions de reinitialisation</t>
+  </si>
+  <si>
+    <t>liaison entre tables de reinitialisation</t>
+  </si>
+  <si>
+    <t>Gestion Import</t>
+  </si>
+  <si>
+    <t>Gestion Commande</t>
+  </si>
+  <si>
+    <t>Creation Interface</t>
+  </si>
+  <si>
+    <t>OrderList</t>
+  </si>
+  <si>
+    <t>Script d'integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OrderList </t>
+  </si>
+  <si>
+    <t>Modification Etat , psUpdateOrderState</t>
+  </si>
+  <si>
+    <t>FrontOffice</t>
+  </si>
+  <si>
+    <t>metier</t>
+  </si>
+  <si>
+    <t>fonctions de liste des products</t>
+  </si>
+  <si>
+    <t>Accueil,gestion produits</t>
+  </si>
+  <si>
+    <t>fonctions psGetProductFullDetails</t>
+  </si>
+  <si>
+    <t>fonctions product_feature_values</t>
+  </si>
+  <si>
+    <t>fonctions product_option_values</t>
+  </si>
+  <si>
+    <t>fonctions combinations</t>
+  </si>
+  <si>
+    <t>fonctions etat setLoggedAdmin</t>
+  </si>
+  <si>
+    <t>gestion emit pour liasons</t>
+  </si>
+  <si>
+    <t>reset.types.ts</t>
+  </si>
+  <si>
+    <t>type de module de system de reinitialisation</t>
+  </si>
+  <si>
+    <t>auth.vue</t>
+  </si>
+  <si>
+    <t>auth-state.js</t>
+  </si>
+  <si>
+    <t>prestashop-api.js</t>
+  </si>
+  <si>
+    <t>App.vue</t>
+  </si>
+  <si>
+    <t>DataResetManager.vue</t>
+  </si>
+  <si>
+    <t>useDataReset.ts</t>
+  </si>
+  <si>
+    <t>reset-modules.config.ts</t>
+  </si>
+  <si>
+    <t>ProductImport.service.ts</t>
+  </si>
+  <si>
+    <t>CombinationImport.service.ts</t>
+  </si>
+  <si>
+    <t>OrderImport.service.ts</t>
+  </si>
+  <si>
+    <t>Import.vue</t>
+  </si>
+  <si>
+    <t>ProductDetail.vue</t>
+  </si>
+  <si>
+    <t>Home.vue</t>
+  </si>
+  <si>
+    <t>ResetReport.vue</t>
+  </si>
+  <si>
+    <t>fonction setStock</t>
+  </si>
+  <si>
+    <t>fonction runCombinationImport</t>
+  </si>
+  <si>
+    <t>Gestion Panier</t>
+  </si>
+  <si>
+    <t>Cart.vue</t>
+  </si>
+  <si>
+    <t>ProductLoadCsv.ts</t>
+  </si>
+  <si>
+    <t>Chargement csv en data[]</t>
+  </si>
+  <si>
+    <t>CombinationLoadCsv.ts</t>
+  </si>
+  <si>
+    <t>OrderImport.ts</t>
+  </si>
+  <si>
+    <t>fonction mapping Etat Order et Payent</t>
+  </si>
+  <si>
+    <t>fonction gestion customer: find /create</t>
+  </si>
+  <si>
+    <t>fonction gestion panier find/create</t>
+  </si>
+  <si>
+    <t>fonction payement et ajout dans panier</t>
+  </si>
+  <si>
+    <t>fonction creation commande, et maj</t>
+  </si>
+  <si>
+    <t>OrderLoadCsv.ts</t>
+  </si>
+  <si>
+    <t>fonction calculatePrix Ht</t>
+  </si>
+  <si>
+    <t>fonction obtention group de taxe</t>
+  </si>
+  <si>
+    <t>fonction de build de xml de produit</t>
+  </si>
+  <si>
+    <t>fonction runProductImport</t>
+  </si>
+  <si>
+    <t>fonction runOrderImport</t>
+  </si>
+  <si>
+    <t>Gestion Import Product</t>
+  </si>
+  <si>
+    <t>Gestion Import Combination</t>
+  </si>
+  <si>
+    <t>Gestion Import Order</t>
+  </si>
+  <si>
+    <t>Gestion Import Image</t>
+  </si>
+  <si>
+    <t>correspondanceImage.ts</t>
+  </si>
+  <si>
+    <t>ImageImport.service.ts</t>
+  </si>
+  <si>
+    <t>cherche nom_fichier % ref de produit</t>
+  </si>
+  <si>
+    <t>dezip et mise a jour image dans prestashop</t>
+  </si>
+  <si>
+    <t>fonction get cle de panier</t>
+  </si>
+  <si>
+    <t>Gestion Achat</t>
+  </si>
+  <si>
+    <t>OrderList.vue</t>
+  </si>
+  <si>
+    <t>Script d'integration chargement Etat</t>
+  </si>
+  <si>
+    <t>Etat Commande</t>
+  </si>
+  <si>
+    <t>Integration de panier ey mise a jour Etat Commande</t>
+  </si>
+  <si>
+    <t>Tableau de bord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">load des commandes by date et calcul des amount </t>
+  </si>
+  <si>
+    <t>Gestion Route</t>
+  </si>
+  <si>
+    <t>Gestion Utilisateur</t>
+  </si>
+  <si>
+    <t>UserPick.vue</t>
+  </si>
+  <si>
+    <t>mise a jour de currentPage pour choix utilisateur</t>
+  </si>
+  <si>
+    <t>Get tous les comptes utilisateurs</t>
+  </si>
+  <si>
+    <t>Fontion de login dynamique selon user choisies</t>
+  </si>
+  <si>
+    <t>Gestion Produit</t>
+  </si>
+  <si>
+    <t>Mise a jour interface</t>
+  </si>
+  <si>
+    <t>fonction de gestion de badge selon date availability</t>
+  </si>
+  <si>
+    <t>Mise a jour interface ajout filtre</t>
+  </si>
+  <si>
+    <t>fonction filtre de produits selon criteres</t>
+  </si>
+  <si>
+    <t>auth-api.js</t>
+  </si>
+  <si>
+    <t>product-api.js</t>
+  </si>
+  <si>
+    <t>Fonction de gestion d'erreur  de fichier</t>
+  </si>
+  <si>
+    <t>Mise a jour d'interface pour les logs</t>
+  </si>
+  <si>
+    <t>Gestion de stock</t>
+  </si>
+  <si>
+    <t>StockManager.vue</t>
+  </si>
+  <si>
+    <t>stock-api.js</t>
+  </si>
+  <si>
+    <t>Ajout champ information stock disponible</t>
+  </si>
+  <si>
+    <t>Existing App</t>
+  </si>
+  <si>
+    <t>StockDelta.php</t>
+  </si>
+  <si>
+    <t>ws_stock_update.php</t>
+  </si>
+  <si>
+    <t>Creation du mouvement de stock endpoint</t>
+  </si>
+  <si>
+    <t>Creation Entite du module de stock et endpoint</t>
+  </si>
+  <si>
+    <t>Appelle de l'endpoint mise a jour stockAvailable</t>
+  </si>
+  <si>
+    <t>Appelle de l'endpoint mise a jour stockByDelta</t>
+  </si>
+  <si>
+    <t>Fonction get stock mvt a partir des commandes</t>
+  </si>
+  <si>
+    <t>chargement des stock et maj quantite</t>
+  </si>
+  <si>
+    <t>Ajout option voir evolution et creation modal</t>
+  </si>
+  <si>
+    <t>Appelle  get stock_deltas et psGetStockMovementsFromOrders</t>
+  </si>
+  <si>
+    <t>Interface graphique</t>
+  </si>
+  <si>
+    <t>Activation du module et cle ws stock update via delta</t>
+  </si>
+  <si>
+    <t>Appelle fonction stock_availables</t>
+  </si>
+  <si>
+    <t>Gestion navigation anonym</t>
+  </si>
+  <si>
+    <t>FoUserPick.vue</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>Champ navigation anonym ou guest</t>
+  </si>
+  <si>
+    <t>gestion et protection pages sans authentification</t>
+  </si>
+  <si>
+    <t>Limit du navigation guest jusqua ce que validation achat</t>
+  </si>
+  <si>
+    <t>Creation module d'authentification au moment validation achat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration  authentification avec compte ou creation </t>
+  </si>
+  <si>
+    <t>Chargement des paniers si authentifie avec compte déjà present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation du commande </t>
+  </si>
+  <si>
+    <t>fonction de gestion de declinaisons</t>
+  </si>
+  <si>
+    <t>fonction get dynamique de taux de tax</t>
+  </si>
+  <si>
+    <t>fonction gestion address</t>
+  </si>
+  <si>
+    <t>Creation du nouveau module qui fonctionne</t>
+  </si>
+  <si>
+    <t>Creation nouveau mise a jour stock qui fonctionne</t>
+  </si>
+  <si>
+    <t>mise a jour etat livre + mvt stock auto</t>
+  </si>
+  <si>
+    <t>OrderList.php</t>
+  </si>
+  <si>
+    <t>Ajout button Livré</t>
+  </si>
+  <si>
+    <t>Statistique</t>
+  </si>
+  <si>
+    <t>Stat.vue</t>
+  </si>
+  <si>
+    <t>Creation d'interface montant vente achat et benefice</t>
+  </si>
+  <si>
+    <t>Scipt d'integration calcul Statistique</t>
+  </si>
+  <si>
+    <t>Creation d'interface statistique tableau par categorie</t>
+  </si>
+  <si>
+    <t>Scipt d'integration tableau par categorie</t>
+  </si>
+  <si>
     <t>(blank)</t>
   </si>
   <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Creation interface</t>
-  </si>
-  <si>
-    <t>ETU003295</t>
-  </si>
-  <si>
-    <t>script de verification</t>
-  </si>
-  <si>
-    <t>Protections Pages</t>
-  </si>
-  <si>
-    <t>mode FO ou BO</t>
-  </si>
-  <si>
-    <t>Layouts separe FO ouBO</t>
-  </si>
-  <si>
-    <t>Gestion Donne</t>
-  </si>
-  <si>
-    <t>fonctions de reinitialisation</t>
-  </si>
-  <si>
-    <t>liaison entre tables de reinitialisation</t>
-  </si>
-  <si>
-    <t>Gestion Import</t>
-  </si>
-  <si>
-    <t>Gestion Commande</t>
-  </si>
-  <si>
-    <t>Creation Interface</t>
-  </si>
-  <si>
-    <t>OrderList</t>
-  </si>
-  <si>
-    <t>Script d'integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OrderList </t>
-  </si>
-  <si>
-    <t>Modification Etat , psUpdateOrderState</t>
-  </si>
-  <si>
-    <t>FrontOffice</t>
-  </si>
-  <si>
-    <t>metier</t>
-  </si>
-  <si>
-    <t>fonctions de liste des products</t>
-  </si>
-  <si>
-    <t>Accueil,gestion produits</t>
-  </si>
-  <si>
-    <t>fonctions psGetProductFullDetails</t>
-  </si>
-  <si>
-    <t>fonctions product_feature_values</t>
-  </si>
-  <si>
-    <t>fonctions product_option_values</t>
-  </si>
-  <si>
-    <t>fonctions combinations</t>
-  </si>
-  <si>
-    <t>fonctions etat setLoggedAdmin</t>
-  </si>
-  <si>
-    <t>gestion emit pour liasons</t>
-  </si>
-  <si>
-    <t>reset.types.ts</t>
-  </si>
-  <si>
-    <t>type de module de system de reinitialisation</t>
-  </si>
-  <si>
-    <t>auth.vue</t>
-  </si>
-  <si>
-    <t>auth-state.js</t>
-  </si>
-  <si>
-    <t>prestashop-api.js</t>
-  </si>
-  <si>
-    <t>App.vue</t>
-  </si>
-  <si>
-    <t>DataResetManager.vue</t>
-  </si>
-  <si>
-    <t>useDataReset.ts</t>
-  </si>
-  <si>
-    <t>reset-modules.config.ts</t>
-  </si>
-  <si>
-    <t>ProductImport.service.ts</t>
-  </si>
-  <si>
-    <t>CombinationImport.service.ts</t>
-  </si>
-  <si>
-    <t>OrderImport.service.ts</t>
-  </si>
-  <si>
-    <t>Import.vue</t>
-  </si>
-  <si>
-    <t>ProductDetail.vue</t>
-  </si>
-  <si>
-    <t>Home.vue</t>
-  </si>
-  <si>
-    <t>ResetReport.vue</t>
-  </si>
-  <si>
-    <t>fonction setStock</t>
-  </si>
-  <si>
-    <t>fonction runCombinationImport</t>
-  </si>
-  <si>
-    <t>Gestion Panier</t>
-  </si>
-  <si>
-    <t>Cart.vue</t>
-  </si>
-  <si>
-    <t>ProductLoadCsv.ts</t>
-  </si>
-  <si>
-    <t>Chargement csv en data[]</t>
-  </si>
-  <si>
-    <t>CombinationLoadCsv.ts</t>
-  </si>
-  <si>
-    <t>OrderImport.ts</t>
-  </si>
-  <si>
-    <t>fonction mapping Etat Order et Payent</t>
-  </si>
-  <si>
-    <t>fonction gestion customer: find /create</t>
-  </si>
-  <si>
-    <t>fonction gestion panier find/create</t>
-  </si>
-  <si>
-    <t>fonction payement et ajout dans panier</t>
-  </si>
-  <si>
-    <t>fonction creation commande, et maj</t>
-  </si>
-  <si>
-    <t>OrderLoadCsv.ts</t>
-  </si>
-  <si>
-    <t>fonction calculatePrix Ht</t>
-  </si>
-  <si>
-    <t>fonction obtention group de taxe</t>
-  </si>
-  <si>
-    <t>fonction de build de xml de produit</t>
-  </si>
-  <si>
-    <t>fonction runProductImport</t>
-  </si>
-  <si>
-    <t>fonction runOrderImport</t>
-  </si>
-  <si>
-    <t>Gestion Import Product</t>
-  </si>
-  <si>
-    <t>Gestion Import Combination</t>
-  </si>
-  <si>
-    <t>Gestion Import Order</t>
-  </si>
-  <si>
-    <t>Gestion Import Image</t>
-  </si>
-  <si>
-    <t>correspondanceImage.ts</t>
-  </si>
-  <si>
-    <t>ImageImport.service.ts</t>
-  </si>
-  <si>
-    <t>cherche nom_fichier % ref de produit</t>
-  </si>
-  <si>
-    <t>dezip et mise a jour image dans prestashop</t>
-  </si>
-  <si>
-    <t>fonction get cle de panier</t>
-  </si>
-  <si>
-    <t>Gestion Achat</t>
-  </si>
-  <si>
-    <t>OrderList.vue</t>
-  </si>
-  <si>
-    <t>Script d'integration chargement Etat</t>
-  </si>
-  <si>
-    <t>Etat Commande</t>
-  </si>
-  <si>
-    <t>Integration de panier ey mise a jour Etat Commande</t>
-  </si>
-  <si>
-    <t>Tableau de bord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">load des commandes by date et calcul des amount </t>
-  </si>
-  <si>
-    <t>Gestion Route</t>
-  </si>
-  <si>
-    <t>Gestion Utilisateur</t>
-  </si>
-  <si>
-    <t>UserPick.vue</t>
-  </si>
-  <si>
-    <t>mise a jour de currentPage pour choix utilisateur</t>
-  </si>
-  <si>
-    <t>Get tous les comptes utilisateurs</t>
-  </si>
-  <si>
-    <t>Fontion de login dynamique selon user choisies</t>
-  </si>
-  <si>
-    <t>Gestion Produit</t>
-  </si>
-  <si>
-    <t>Mise a jour interface</t>
-  </si>
-  <si>
-    <t>fonction de gestion de badge selon date availability</t>
-  </si>
-  <si>
-    <t>Mise a jour interface ajout filtre</t>
-  </si>
-  <si>
-    <t>fonction filtre de produits selon criteres</t>
-  </si>
-  <si>
-    <t>auth-api.js</t>
-  </si>
-  <si>
-    <t>product-api.js</t>
-  </si>
-  <si>
-    <t>Fonction de gestion d'erreur  de fichier</t>
-  </si>
-  <si>
-    <t>Mise a jour d'interface pour les logs</t>
-  </si>
-  <si>
-    <t>Gestion de stock</t>
-  </si>
-  <si>
-    <t>StockManager.vue</t>
-  </si>
-  <si>
-    <t>stock-api.js</t>
-  </si>
-  <si>
-    <t>Ajout champ information stock disponible</t>
-  </si>
-  <si>
-    <t>Existing App</t>
-  </si>
-  <si>
-    <t>StockDelta.php</t>
-  </si>
-  <si>
-    <t>ws_stock_update.php</t>
-  </si>
-  <si>
-    <t>Creation du mouvement de stock endpoint</t>
-  </si>
-  <si>
-    <t>Creation Entite du module de stock et endpoint</t>
-  </si>
-  <si>
-    <t>Appelle de l'endpoint mise a jour stockAvailable</t>
-  </si>
-  <si>
-    <t>Appelle de l'endpoint mise a jour stockByDelta</t>
-  </si>
-  <si>
-    <t>Fonction get stock mvt a partir des commandes</t>
-  </si>
-  <si>
-    <t>chargement des stock et maj quantite</t>
-  </si>
-  <si>
-    <t>Ajout option voir evolution et creation modal</t>
-  </si>
-  <si>
-    <t>Appelle  get stock_deltas et psGetStockMovementsFromOrders</t>
-  </si>
-  <si>
-    <t>Interface graphique</t>
-  </si>
-  <si>
-    <t>Activation du module et cle ws stock update via delta</t>
-  </si>
-  <si>
-    <t>Appelle fonction stock_availables</t>
-  </si>
-  <si>
-    <t>Gestion navigation anonym</t>
-  </si>
-  <si>
-    <t>FoUserPick.vue</t>
-  </si>
-  <si>
-    <t>Interface</t>
-  </si>
-  <si>
-    <t>Champ navigation anonym ou guest</t>
-  </si>
-  <si>
-    <t>gestion et protection pages sans authentification</t>
-  </si>
-  <si>
-    <t>Limit du navigation guest jusqua ce que validation achat</t>
-  </si>
-  <si>
-    <t>Creation module d'authentification au moment validation achat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration  authentification avec compte ou creation </t>
-  </si>
-  <si>
-    <t>Chargement des paniers si authentifie avec compte déjà present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalisation du commande </t>
-  </si>
-  <si>
-    <t>fonction de gestion de declinaisons</t>
-  </si>
-  <si>
-    <t>fonction get dynamique de taux de tax</t>
-  </si>
-  <si>
-    <t>fonction gestion address</t>
   </si>
 </sst>
 </file>
@@ -801,18 +834,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -835,7 +868,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46159.800975347222" refreshedVersion="8" recordCount="85" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46161.386780092595" refreshedVersion="8" recordCount="102" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K1006" sheet="liste des taches"/>
   </cacheSource>
@@ -856,12 +889,18 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Qui" numFmtId="0">
-      <sharedItems containsBlank="1" count="9">
+      <sharedItems containsBlank="1" count="15">
         <s v="ETU003295"/>
         <m/>
         <s v="ETU003296" u="1"/>
         <s v="ETU003297" u="1"/>
         <s v="ETU003298" u="1"/>
+        <s v="ETU003299" u="1"/>
+        <s v="ETU003300" u="1"/>
+        <s v="ETU003301" u="1"/>
+        <s v="ETU003302" u="1"/>
+        <s v="ETU003303" u="1"/>
+        <s v="ETU003304" u="1"/>
         <s v="ETU00YYYY" u="1"/>
         <s v="ETU00XXXX" u="1"/>
         <s v="ETU00ZZZZ" u="1"/>
@@ -869,10 +908,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Estimation" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="100" maxValue="100"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="45"/>
     </cacheField>
     <cacheField name="Temps passé" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="100" maxValue="100"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="45"/>
     </cacheField>
     <cacheField name="Reste à faire" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
@@ -890,7 +929,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="85">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="102">
   <r>
     <s v="Backoffice"/>
     <s v="Gestion Login"/>
@@ -898,8 +937,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -910,8 +949,8 @@
     <s v="fonctions etat setLoggedAdmin"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="5"/>
+    <n v="5"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -922,8 +961,8 @@
     <s v="checkLogin"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="5"/>
+    <n v="5"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -934,8 +973,8 @@
     <s v="script de verification"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -946,8 +985,8 @@
     <s v="Layouts separe FO ouBO"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -958,8 +997,8 @@
     <s v="mode FO ou BO"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -970,8 +1009,8 @@
     <s v="gestion emit pour liasons"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -982,8 +1021,8 @@
     <s v="type de module de system de reinitialisation"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -994,8 +1033,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1006,8 +1045,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1018,8 +1057,8 @@
     <s v="fonctions de reinitialisation"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1030,8 +1069,8 @@
     <s v="liaison entre tables de reinitialisation"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1042,8 +1081,8 @@
     <s v="fonction calculatePrix Ht"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1054,8 +1093,8 @@
     <s v="fonction obtention group de taxe"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1066,8 +1105,8 @@
     <s v="fonction de build de xml de produit"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1078,8 +1117,8 @@
     <s v="fonction runProductImport"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1090,8 +1129,8 @@
     <s v="Chargement csv en data[]"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1099,11 +1138,11 @@
     <s v="Backoffice"/>
     <s v="Gestion Import Combination"/>
     <s v="CombinationImport.service.ts"/>
-    <s v="fonction getDynamicTaxRate"/>
+    <s v="fonction get dynamique de taux de tax"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1111,11 +1150,11 @@
     <s v="Backoffice"/>
     <s v="Gestion Import Combination"/>
     <s v="CombinationImport.service.ts"/>
-    <s v="fonction ensureAttrAndVal"/>
+    <s v="fonction de gestion de declinaisons"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1126,8 +1165,8 @@
     <s v="fonction setStock"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1138,8 +1177,8 @@
     <s v="fonction runCombinationImport"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1150,8 +1189,8 @@
     <s v="Chargement csv en data[]"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1162,8 +1201,8 @@
     <s v="fonction gestion customer: find /create"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1174,8 +1213,8 @@
     <s v="fonction mapping Etat Order et Payent"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1183,11 +1222,11 @@
     <s v="Backoffice"/>
     <s v="Gestion Import Order"/>
     <s v="OrderImport.ts"/>
-    <s v="fonction gestion customer: find /create"/>
+    <s v="fonction gestion address"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1198,8 +1237,8 @@
     <s v="fonction gestion panier find/create"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1210,8 +1249,8 @@
     <s v="fonction payement et ajout dans panier"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="45"/>
+    <n v="45"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1222,8 +1261,8 @@
     <s v="fonction creation commande, et maj"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="45"/>
+    <n v="45"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1234,8 +1273,8 @@
     <s v="fonction runOrderImport"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1246,8 +1285,8 @@
     <s v="Chargement csv en data[]"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="45"/>
+    <n v="45"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1258,8 +1297,8 @@
     <s v="cherche nom_fichier % ref de produit"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1270,8 +1309,8 @@
     <s v="dezip et mise a jour image dans prestashop"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1282,8 +1321,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1294,8 +1333,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1306,8 +1345,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1318,8 +1357,8 @@
     <s v="Modification Etat , psUpdateOrderState"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1330,8 +1369,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1342,8 +1381,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1354,8 +1393,8 @@
     <s v="fonctions de liste des products"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1366,8 +1405,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1378,8 +1417,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1390,8 +1429,8 @@
     <s v="fonctions product_feature_values"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1402,8 +1441,8 @@
     <s v="fonctions product_option_values"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1414,8 +1453,8 @@
     <s v="fonctions combinations"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1426,8 +1465,8 @@
     <s v="fonctions psGetProductFullDetails"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1438,8 +1477,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1450,8 +1489,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1462,8 +1501,8 @@
     <s v="fonction get cle de panier"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1474,8 +1513,8 @@
     <s v="fonction gestion panier find/create"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1486,8 +1525,8 @@
     <s v="fonction creation commande, et maj"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="45"/>
+    <n v="45"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1498,8 +1537,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1510,8 +1549,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1522,8 +1561,8 @@
     <s v="Script d'integration chargement Etat"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1534,8 +1573,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1546,8 +1585,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1558,8 +1597,8 @@
     <s v="Integration de panier ey mise a jour Etat Commande"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="45"/>
+    <n v="45"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1570,8 +1609,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1582,8 +1621,8 @@
     <s v="load des commandes by date et calcul des amount "/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="40"/>
+    <n v="40"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1594,8 +1633,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1606,8 +1645,8 @@
     <s v="mise a jour de currentPage pour choix utilisateur"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1615,11 +1654,11 @@
     <s v="FrontOffice"/>
     <s v="Gestion Route"/>
     <s v="App.vue"/>
-    <s v="gestion et protection pages pour iutilisateur anonym"/>
+    <s v="gestion et protection pages sans authentification"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1630,8 +1669,8 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1642,8 +1681,8 @@
     <s v="Get tous les comptes utilisateurs"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1654,8 +1693,8 @@
     <s v="Fontion de login dynamique selon user choisies"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1666,8 +1705,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1678,8 +1717,8 @@
     <s v="Mise a jour interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1690,8 +1729,8 @@
     <s v="fonction de gestion de badge selon date availability"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1702,8 +1741,8 @@
     <s v="Script d'integration"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1714,8 +1753,8 @@
     <s v="Mise a jour interface ajout filtre"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1726,8 +1765,8 @@
     <s v="fonction filtre de produits selon criteres"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1738,8 +1777,8 @@
     <s v="Fonction de gestion d'erreur  de fichier"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1750,8 +1789,8 @@
     <s v="Fonction de gestion d'erreur  de fichier"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1762,8 +1801,8 @@
     <s v="Fonction de gestion d'erreur  de fichier"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1774,8 +1813,80 @@
     <s v="Mise a jour d'interface pour les logs"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion navigation anonym"/>
+    <s v="FoUserPick.vue"/>
+    <s v="Champ navigation anonym ou guest"/>
+    <s v="Interface"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion navigation anonym"/>
+    <s v="App.vue"/>
+    <s v="Limit du navigation guest jusqua ce que validation achat"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="25"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion navigation anonym"/>
+    <s v="Cart.vue"/>
+    <s v="Creation module d'authentification au moment validation achat"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion navigation anonym"/>
+    <s v="Cart.vue"/>
+    <s v="Integration  authentification avec compte ou creation "/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="40"/>
+    <n v="40"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion navigation anonym"/>
+    <s v="Cart.vue"/>
+    <s v="Chargement des paniers si authentifie avec compte déjà present"/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="FrontOffice"/>
+    <s v="Gestion navigation anonym"/>
+    <s v="Cart.vue"/>
+    <s v="Finalisation du commande "/>
+    <s v="Integration"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1786,8 +1897,44 @@
     <s v="Creation interface"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Existing App"/>
+    <s v="Gestion de stock"/>
+    <s v="StockDelta.php"/>
+    <s v="Creation Entite du module de stock et endpoint"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Existing App"/>
+    <s v="Gestion de stock"/>
+    <s v="ws_stock_update.php"/>
+    <s v="Creation du mouvement de stock endpoint"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Existing App"/>
+    <s v="Gestion de stock"/>
+    <s v="Interface graphique"/>
+    <s v="Activation du module et cle ws stock update via delta"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1795,11 +1942,35 @@
     <s v="Backoffice"/>
     <s v="Gestion de stock"/>
     <s v="stock-api.js"/>
-    <s v="Fonction de mouvements de stock"/>
+    <s v="Appelle de l'endpoint mise a jour stockAvailable"/>
     <s v="Metier"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="stock-api.js"/>
+    <s v="Appelle de l'endpoint mise a jour stockByDelta"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="stock-api.js"/>
+    <s v="Fonction get stock mvt a partir des commandes"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1807,11 +1978,11 @@
     <s v="Backoffice"/>
     <s v="Gestion de stock"/>
     <s v="StockManager.vue"/>
-    <s v="Script d'integration"/>
+    <s v="chargement des stock et maj quantite"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1819,23 +1990,11 @@
     <s v="Backoffice"/>
     <s v="Gestion de stock"/>
     <s v="StockManager.vue"/>
-    <s v="Amelioration d'interface (petite dashboard d'evolution)"/>
+    <s v="Ajout option voir evolution et creation modal"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion de stock"/>
-    <s v="stock-api.js"/>
-    <s v="Fonction filtre selon date et mouvement"/>
-    <s v="Metier"/>
-    <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1843,23 +2002,11 @@
     <s v="Backoffice"/>
     <s v="Gestion de stock"/>
     <s v="StockManager.vue"/>
-    <s v="Script d'integration"/>
+    <s v="Appelle  get stock_deltas et psGetStockMovementsFromOrders"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <s v="Backoffice"/>
-    <s v="Gestion de stock"/>
-    <s v="stock-api.js"/>
-    <s v="Fonction filtre selon date et mouvement"/>
-    <s v="Metier"/>
-    <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="30"/>
+    <n v="30"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1870,20 +2017,8 @@
     <s v="Ajout champ information stock disponible"/>
     <s v="Affichage"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
-    <n v="0"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <s v="FrontOffice"/>
-    <s v="Gestion de stock"/>
-    <s v="stock-api.js"/>
-    <s v="Fonction de get de stock disponible"/>
-    <s v="Metier"/>
-    <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="5"/>
+    <n v="5"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1891,11 +2026,119 @@
     <s v="FrontOffice"/>
     <s v="Gestion de stock"/>
     <s v="ProductDetail.vue"/>
-    <s v="Get et Affichage de stock dispo"/>
+    <s v="Appelle fonction stock_availables"/>
     <s v="Integration"/>
     <x v="0"/>
-    <n v="100"/>
-    <n v="100"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Existing App"/>
+    <s v="Gestion de stock"/>
+    <s v="ws_stock_update.php"/>
+    <s v="Creation du nouveau module qui fonctionne"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="product-api.js"/>
+    <s v="Creation nouveau mise a jour stock qui fonctionne"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="OrderImport.ts"/>
+    <s v="mise a jour etat livre + mvt stock auto"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="OrderList.php"/>
+    <s v="mise a jour etat livre + mvt stock auto"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Gestion de stock"/>
+    <s v="OrderList.php"/>
+    <s v="Ajout button Livré"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Statistique"/>
+    <s v="Stat.vue"/>
+    <s v="Creation d'interface montant vente achat et benefice"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="15"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Statistique"/>
+    <s v="Stat.vue"/>
+    <s v="Scipt d'integration calcul Statistique"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="25"/>
+    <n v="25"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Statistique"/>
+    <s v="Stat.vue"/>
+    <s v="Creation d'interface statistique tableau par categorie"/>
+    <s v="Affichage"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Backoffice"/>
+    <s v="Statistique"/>
+    <s v="Stat.vue"/>
+    <s v="Scipt d'integration tableau par categorie"/>
+    <s v="Metier"/>
+    <x v="0"/>
+    <n v="25"/>
+    <n v="25"/>
     <n v="0"/>
     <n v="1"/>
   </r>
@@ -1924,15 +2167,21 @@
     <pivotField name="Description tâche" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Type" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Qui" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items count="10">
+      <items count="16">
         <item x="0"/>
         <item m="1" x="2"/>
         <item m="1" x="3"/>
         <item m="1" x="4"/>
+        <item m="1" x="5"/>
+        <item m="1" x="6"/>
+        <item m="1" x="7"/>
         <item m="1" x="8"/>
-        <item m="1" x="6"/>
-        <item m="1" x="5"/>
-        <item m="1" x="7"/>
+        <item m="1" x="9"/>
+        <item m="1" x="10"/>
+        <item m="1" x="14"/>
+        <item m="1" x="12"/>
+        <item m="1" x="11"/>
+        <item m="1" x="13"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -1950,7 +2199,7 @@
       <x/>
     </i>
     <i>
-      <x v="8"/>
+      <x v="14"/>
     </i>
     <i t="grand">
       <x/>
@@ -2190,7 +2439,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2230,7 +2479,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -2285,17 +2534,17 @@
       <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="29" t="s">
-        <v>64</v>
+      <c r="D2" s="28" t="s">
+        <v>62</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="29" t="s">
-        <v>37</v>
+      <c r="G2" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H2" s="6">
         <v>10</v>
@@ -2323,17 +2572,17 @@
       <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="29" t="s">
-        <v>65</v>
+      <c r="D3" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="29" t="s">
-        <v>37</v>
+      <c r="G3" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H3" s="6">
         <v>5</v>
@@ -2361,8 +2610,8 @@
       <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>124</v>
+      <c r="D4" s="28" t="s">
+        <v>122</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>21</v>
@@ -2370,8 +2619,8 @@
       <c r="F4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="29" t="s">
-        <v>37</v>
+      <c r="G4" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H4" s="6">
         <v>5</v>
@@ -2399,17 +2648,17 @@
       <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>64</v>
+      <c r="D5" s="28" t="s">
+        <v>62</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>37</v>
+      <c r="G5" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H5" s="6">
         <v>10</v>
@@ -2435,19 +2684,19 @@
         <v>17</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="29" t="s">
-        <v>37</v>
+      <c r="G6" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H6" s="6">
         <v>15</v>
@@ -2473,19 +2722,19 @@
         <v>17</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>67</v>
+        <v>37</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>37</v>
+      <c r="G7" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H7" s="6">
         <v>10</v>
@@ -2511,19 +2760,19 @@
         <v>17</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>67</v>
+        <v>37</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>37</v>
+      <c r="G8" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H8" s="6">
         <v>15</v>
@@ -2549,19 +2798,19 @@
         <v>17</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>60</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>37</v>
+      <c r="G9" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H9" s="6">
         <v>15</v>
@@ -2587,19 +2836,19 @@
         <v>17</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>77</v>
+        <v>40</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="29" t="s">
-        <v>37</v>
+      <c r="G10" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H10" s="6">
         <v>10</v>
@@ -2625,19 +2874,19 @@
         <v>17</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>68</v>
+        <v>40</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>66</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="29" t="s">
-        <v>37</v>
+      <c r="G11" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H11" s="6">
         <v>10</v>
@@ -2663,19 +2912,19 @@
         <v>17</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>69</v>
+        <v>40</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>67</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="29" t="s">
-        <v>37</v>
+      <c r="G12" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H12" s="6">
         <v>25</v>
@@ -2701,19 +2950,19 @@
         <v>17</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="29" t="s">
-        <v>37</v>
+      <c r="G13" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H13" s="6">
         <v>20</v>
@@ -2739,19 +2988,19 @@
         <v>17</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>37</v>
+      <c r="G14" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H14" s="6">
         <v>15</v>
@@ -2777,19 +3026,19 @@
         <v>17</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="29" t="s">
-        <v>37</v>
+      <c r="G15" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H15" s="6">
         <v>20</v>
@@ -2815,19 +3064,19 @@
         <v>17</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="29" t="s">
-        <v>37</v>
+      <c r="G16" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H16" s="6">
         <v>20</v>
@@ -2853,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>71</v>
+        <v>95</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="29" t="s">
-        <v>37</v>
+      <c r="G17" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H17" s="6">
         <v>25</v>
@@ -2891,19 +3140,19 @@
         <v>17</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>82</v>
+        <v>95</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>80</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="29" t="s">
-        <v>37</v>
+      <c r="G18" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H18" s="6">
         <v>20</v>
@@ -2929,19 +3178,19 @@
         <v>17</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>72</v>
+        <v>96</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="29" t="s">
-        <v>37</v>
+      <c r="G19" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H19" s="6">
         <v>25</v>
@@ -2967,19 +3216,19 @@
         <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>72</v>
+        <v>96</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="29" t="s">
-        <v>37</v>
+      <c r="G20" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H20" s="6">
         <v>30</v>
@@ -3005,19 +3254,19 @@
         <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>72</v>
+        <v>96</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="29" t="s">
-        <v>37</v>
+      <c r="G21" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H21" s="6">
         <v>10</v>
@@ -3043,19 +3292,19 @@
         <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>72</v>
+        <v>96</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="29" t="s">
-        <v>37</v>
+      <c r="G22" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H22" s="6">
         <v>30</v>
@@ -3081,19 +3330,19 @@
         <v>17</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>84</v>
+        <v>96</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="29" t="s">
-        <v>37</v>
+      <c r="G23" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H23" s="6">
         <v>30</v>
@@ -3119,19 +3368,19 @@
         <v>17</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="F24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="29" t="s">
-        <v>37</v>
+      <c r="G24" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H24" s="6">
         <v>15</v>
@@ -3157,19 +3406,19 @@
         <v>17</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>85</v>
+        <v>97</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="29" t="s">
-        <v>37</v>
+      <c r="G25" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H25" s="6">
         <v>30</v>
@@ -3195,19 +3444,19 @@
         <v>17</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>85</v>
+        <v>97</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="29" t="s">
-        <v>37</v>
+      <c r="G26" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H26" s="6">
         <v>10</v>
@@ -3233,19 +3482,19 @@
         <v>17</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>73</v>
+        <v>97</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="29" t="s">
-        <v>37</v>
+      <c r="G27" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H27" s="6">
         <v>25</v>
@@ -3271,19 +3520,19 @@
         <v>17</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>73</v>
+        <v>97</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>37</v>
+      <c r="G28" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H28" s="6">
         <v>45</v>
@@ -3309,19 +3558,19 @@
         <v>17</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>73</v>
+        <v>97</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="29" t="s">
-        <v>37</v>
+      <c r="G29" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H29" s="6">
         <v>45</v>
@@ -3347,19 +3596,19 @@
         <v>17</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>73</v>
+        <v>97</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>71</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="29" t="s">
-        <v>37</v>
+      <c r="G30" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H30" s="6">
         <v>30</v>
@@ -3385,19 +3634,19 @@
         <v>17</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>89</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="29" t="s">
-        <v>37</v>
+      <c r="G31" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H31" s="6">
         <v>45</v>
@@ -3423,19 +3672,19 @@
         <v>17</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="29" t="s">
-        <v>37</v>
+      <c r="G32" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H32" s="6">
         <v>10</v>
@@ -3461,19 +3710,19 @@
         <v>17</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="E33" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="29" t="s">
-        <v>37</v>
+      <c r="G33" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H33" s="6">
         <v>15</v>
@@ -3499,19 +3748,19 @@
         <v>17</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G34" s="29" t="s">
-        <v>37</v>
+      <c r="G34" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H34" s="6">
         <v>15</v>
@@ -3537,19 +3786,19 @@
         <v>17</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="29" t="s">
-        <v>37</v>
+      <c r="G35" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H35" s="6">
         <v>25</v>
@@ -3575,19 +3824,19 @@
         <v>17</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="29" t="s">
-        <v>48</v>
-      </c>
       <c r="E36" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="29" t="s">
-        <v>37</v>
+      <c r="G36" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H36" s="6">
         <v>30</v>
@@ -3613,19 +3862,19 @@
         <v>17</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>125</v>
+        <v>44</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="29" t="s">
-        <v>37</v>
+      <c r="G37" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H37" s="6">
         <v>20</v>
@@ -3651,19 +3900,19 @@
         <v>17</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>48</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>37</v>
+      <c r="G38" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H38" s="6">
         <v>15</v>
@@ -3686,22 +3935,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>76</v>
+        <v>53</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="29" t="s">
-        <v>37</v>
+      <c r="G39" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H39" s="6">
         <v>15</v>
@@ -3724,22 +3973,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G40" s="29" t="s">
-        <v>37</v>
+        <v>51</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H40" s="6">
         <v>15</v>
@@ -3762,22 +4011,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>76</v>
+        <v>53</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G41" s="29" t="s">
-        <v>37</v>
+      <c r="G41" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H41" s="6">
         <v>20</v>
@@ -3800,22 +4049,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>75</v>
+        <v>53</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>73</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G42" s="29" t="s">
-        <v>37</v>
+      <c r="G42" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H42" s="6">
         <v>25</v>
@@ -3838,22 +4087,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="F43" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G43" s="29" t="s">
-        <v>37</v>
+      <c r="G43" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H43" s="6">
         <v>25</v>
@@ -3876,22 +4125,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>125</v>
+        <v>53</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="29" t="s">
-        <v>37</v>
+      <c r="G44" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H44" s="6">
         <v>30</v>
@@ -3914,22 +4163,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>125</v>
+        <v>53</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G45" s="29" t="s">
-        <v>37</v>
+      <c r="G45" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H45" s="6">
         <v>30</v>
@@ -3952,22 +4201,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>125</v>
+        <v>53</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G46" s="29" t="s">
-        <v>37</v>
+      <c r="G46" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H46" s="6">
         <v>25</v>
@@ -3990,22 +4239,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>75</v>
+        <v>53</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>73</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="29" t="s">
-        <v>37</v>
+      <c r="G47" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H47" s="6">
         <v>25</v>
@@ -4028,22 +4277,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G48" s="29" t="s">
-        <v>37</v>
+      <c r="G48" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H48" s="6">
         <v>30</v>
@@ -4066,22 +4315,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>125</v>
+        <v>78</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G49" s="29" t="s">
-        <v>37</v>
+      <c r="G49" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H49" s="6">
         <v>15</v>
@@ -4104,22 +4353,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>125</v>
+        <v>78</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="29" t="s">
-        <v>37</v>
+      <c r="G50" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H50" s="6">
         <v>25</v>
@@ -4142,22 +4391,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="29" t="s">
-        <v>37</v>
+      <c r="G51" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H51" s="6">
         <v>45</v>
@@ -4180,22 +4429,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>81</v>
+        <v>104</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G52" s="29" t="s">
-        <v>37</v>
+      <c r="G52" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H52" s="6">
         <v>20</v>
@@ -4218,22 +4467,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>107</v>
+        <v>44</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>105</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G53" s="29" t="s">
-        <v>37</v>
+      <c r="G53" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H53" s="6">
         <v>15</v>
@@ -4256,22 +4505,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>107</v>
+        <v>44</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>105</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="29" t="s">
-        <v>37</v>
+      <c r="G54" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H54" s="6">
         <v>30</v>
@@ -4296,20 +4545,20 @@
       <c r="B55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D55" s="29" t="s">
+      <c r="C55" s="28" t="s">
         <v>107</v>
       </c>
+      <c r="D55" s="28" t="s">
+        <v>105</v>
+      </c>
       <c r="E55" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="29" t="s">
-        <v>37</v>
+      <c r="G55" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H55" s="6">
         <v>15</v>
@@ -4334,20 +4583,20 @@
       <c r="B56" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="29" t="s">
+      <c r="C56" s="28" t="s">
         <v>107</v>
       </c>
+      <c r="D56" s="28" t="s">
+        <v>105</v>
+      </c>
       <c r="E56" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="29" t="s">
-        <v>37</v>
+      <c r="G56" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H56" s="6">
         <v>20</v>
@@ -4372,20 +4621,20 @@
       <c r="B57" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>125</v>
+      <c r="C57" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G57" s="29" t="s">
-        <v>37</v>
+      <c r="G57" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H57" s="6">
         <v>45</v>
@@ -4410,20 +4659,20 @@
       <c r="B58" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>76</v>
+      <c r="C58" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G58" s="29" t="s">
-        <v>37</v>
+      <c r="G58" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H58" s="6">
         <v>20</v>
@@ -4448,20 +4697,20 @@
       <c r="B59" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>125</v>
+      <c r="C59" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G59" s="29" t="s">
-        <v>37</v>
+      <c r="G59" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H59" s="6">
         <v>40</v>
@@ -4486,20 +4735,20 @@
       <c r="B60" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>76</v>
+      <c r="C60" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G60" s="29" t="s">
-        <v>37</v>
+      <c r="G60" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H60" s="6">
         <v>20</v>
@@ -4522,22 +4771,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>67</v>
+        <v>111</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G61" s="29" t="s">
-        <v>37</v>
+      <c r="G61" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H61" s="6">
         <v>20</v>
@@ -4560,22 +4809,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D62" s="29" t="s">
-        <v>67</v>
+        <v>111</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G62" s="29" t="s">
-        <v>37</v>
+      <c r="G62" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H62" s="6">
         <v>15</v>
@@ -4598,22 +4847,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>113</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G63" s="29" t="s">
-        <v>37</v>
+      <c r="G63" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H63" s="6">
         <v>20</v>
@@ -4636,22 +4885,22 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>122</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="29" t="s">
-        <v>37</v>
+      <c r="G64" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H64" s="6">
         <v>10</v>
@@ -4674,22 +4923,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="29" t="s">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>122</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G65" s="29" t="s">
-        <v>37</v>
+      <c r="G65" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H65" s="6">
         <v>15</v>
@@ -4712,22 +4961,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" s="29" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>113</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G66" s="29" t="s">
-        <v>37</v>
+      <c r="G66" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H66" s="6">
         <v>15</v>
@@ -4750,22 +4999,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>76</v>
+        <v>117</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G67" s="29" t="s">
-        <v>37</v>
+      <c r="G67" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H67" s="6">
         <v>15</v>
@@ -4788,22 +5037,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E68" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="F68" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G68" s="29" t="s">
-        <v>37</v>
+      <c r="G68" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H68" s="6">
         <v>10</v>
@@ -4826,22 +5075,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>76</v>
+        <v>117</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G69" s="29" t="s">
-        <v>37</v>
+      <c r="G69" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H69" s="6">
         <v>15</v>
@@ -4864,22 +5113,22 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>76</v>
+        <v>117</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G70" s="29" t="s">
-        <v>37</v>
+      <c r="G70" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H70" s="6">
         <v>15</v>
@@ -4902,22 +5151,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>76</v>
+        <v>117</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>74</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G71" s="29" t="s">
-        <v>37</v>
+      <c r="G71" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H71" s="6">
         <v>20</v>
@@ -4943,19 +5192,19 @@
         <v>17</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D72" s="29" t="s">
-        <v>82</v>
+        <v>95</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>80</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G72" s="29" t="s">
-        <v>37</v>
+      <c r="G72" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H72" s="6">
         <v>10</v>
@@ -4981,19 +5230,19 @@
         <v>17</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D73" s="29" t="s">
-        <v>84</v>
+        <v>96</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G73" s="29" t="s">
-        <v>37</v>
+      <c r="G73" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H73" s="6">
         <v>10</v>
@@ -5019,19 +5268,19 @@
         <v>17</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D74" s="29" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>89</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G74" s="29" t="s">
-        <v>37</v>
+      <c r="G74" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H74" s="6">
         <v>10</v>
@@ -5057,19 +5306,19 @@
         <v>17</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D75" s="29" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="D75" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="29" t="s">
-        <v>37</v>
+      <c r="G75" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H75" s="6">
         <v>15</v>
@@ -5092,22 +5341,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F76" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D76" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="G76" s="29" t="s">
-        <v>37</v>
+      <c r="G76" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H76" s="6">
         <v>15</v>
@@ -5130,22 +5379,22 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>67</v>
+        <v>144</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G77" s="29" t="s">
-        <v>37</v>
+      <c r="G77" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H77" s="6">
         <v>25</v>
@@ -5168,22 +5417,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D78" s="29" t="s">
-        <v>81</v>
+        <v>144</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G78" s="29" t="s">
-        <v>37</v>
+      <c r="G78" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H78" s="6">
         <v>30</v>
@@ -5206,22 +5455,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>81</v>
+        <v>144</v>
+      </c>
+      <c r="D79" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G79" s="29" t="s">
-        <v>37</v>
+      <c r="G79" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H79" s="6">
         <v>40</v>
@@ -5244,22 +5493,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D80" s="29" t="s">
-        <v>81</v>
+        <v>144</v>
+      </c>
+      <c r="D80" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G80" s="29" t="s">
-        <v>37</v>
+      <c r="G80" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H80" s="6">
         <v>45</v>
@@ -5282,22 +5531,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D81" s="29" t="s">
-        <v>81</v>
+        <v>144</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G81" s="29" t="s">
-        <v>37</v>
+      <c r="G81" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H81" s="6">
         <v>30</v>
@@ -5323,19 +5572,19 @@
         <v>17</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D82" s="29" t="s">
-        <v>129</v>
+        <v>126</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>127</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G82" s="29" t="s">
-        <v>37</v>
+      <c r="G82" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H82" s="6">
         <v>20</v>
@@ -5358,22 +5607,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D83" s="29" t="s">
-        <v>133</v>
+        <v>126</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>131</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G83" s="29" t="s">
-        <v>37</v>
+      <c r="G83" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H83" s="6">
         <v>20</v>
@@ -5396,22 +5645,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D84" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="C84" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D84" s="29" t="s">
-        <v>134</v>
-      </c>
       <c r="E84" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G84" s="29" t="s">
-        <v>37</v>
+      <c r="G84" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H84" s="6">
         <v>15</v>
@@ -5434,22 +5683,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D85" s="29" t="s">
-        <v>143</v>
+        <v>126</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>141</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G85" s="29" t="s">
-        <v>37</v>
+      <c r="G85" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H85" s="6">
         <v>2</v>
@@ -5475,19 +5724,19 @@
         <v>17</v>
       </c>
       <c r="C86" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D86" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="D86" s="29" t="s">
-        <v>130</v>
-      </c>
       <c r="E86" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G86" s="29" t="s">
-        <v>37</v>
+      <c r="G86" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H86" s="6">
         <v>15</v>
@@ -5513,19 +5762,19 @@
         <v>17</v>
       </c>
       <c r="C87" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="D87" s="29" t="s">
-        <v>130</v>
-      </c>
       <c r="E87" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G87" s="29" t="s">
-        <v>37</v>
+      <c r="G87" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H87" s="6">
         <v>15</v>
@@ -5551,19 +5800,19 @@
         <v>17</v>
       </c>
       <c r="C88" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="D88" s="29" t="s">
-        <v>130</v>
-      </c>
       <c r="E88" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G88" s="29" t="s">
-        <v>37</v>
+      <c r="G88" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H88" s="6">
         <v>30</v>
@@ -5589,19 +5838,19 @@
         <v>17</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D89" s="29" t="s">
-        <v>129</v>
+        <v>126</v>
+      </c>
+      <c r="D89" s="28" t="s">
+        <v>127</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G89" s="29" t="s">
-        <v>37</v>
+      <c r="G89" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H89" s="6">
         <v>30</v>
@@ -5627,19 +5876,19 @@
         <v>17</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D90" s="29" t="s">
-        <v>129</v>
+        <v>126</v>
+      </c>
+      <c r="D90" s="28" t="s">
+        <v>127</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G90" s="29" t="s">
-        <v>37</v>
+      <c r="G90" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H90" s="6">
         <v>20</v>
@@ -5665,19 +5914,19 @@
         <v>17</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D91" s="29" t="s">
-        <v>129</v>
+        <v>126</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>127</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G91" s="29" t="s">
-        <v>37</v>
+      <c r="G91" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H91" s="6">
         <v>30</v>
@@ -5700,22 +5949,22 @@
         <v>91</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D92" s="29" t="s">
-        <v>75</v>
+        <v>126</v>
+      </c>
+      <c r="D92" s="28" t="s">
+        <v>73</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G92" s="29" t="s">
-        <v>37</v>
+      <c r="G92" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H92" s="6">
         <v>5</v>
@@ -5738,22 +5987,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D93" s="29" t="s">
-        <v>75</v>
+        <v>126</v>
+      </c>
+      <c r="D93" s="28" t="s">
+        <v>73</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G93" s="29" t="s">
-        <v>37</v>
+      <c r="G93" s="28" t="s">
+        <v>35</v>
       </c>
       <c r="H93" s="6">
         <v>15</v>
@@ -5768,6 +6017,348 @@
       </c>
       <c r="K93" s="9">
         <f>(I93/(I93+J93))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="12.75">
+      <c r="A94" s="5">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H94" s="6">
+        <v>20</v>
+      </c>
+      <c r="I94" s="6">
+        <f t="shared" ref="I94" si="58">H94</f>
+        <v>20</v>
+      </c>
+      <c r="J94" s="8">
+        <f t="shared" ref="J94" si="59">H94-I94</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="9">
+        <f t="shared" ref="K94" si="60">(I94/(I94+J94))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="12.75">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H95" s="6">
+        <v>10</v>
+      </c>
+      <c r="I95" s="6">
+        <f t="shared" ref="I95:I98" si="61">H95</f>
+        <v>10</v>
+      </c>
+      <c r="J95" s="8">
+        <f t="shared" ref="J95:J98" si="62">H95-I95</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="9">
+        <f t="shared" ref="K95:K98" si="63">(I95/(I95+J95))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="12.75">
+      <c r="A96" s="5">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D96" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H96" s="6">
+        <v>10</v>
+      </c>
+      <c r="I96" s="6">
+        <f t="shared" si="61"/>
+        <v>10</v>
+      </c>
+      <c r="J96" s="8">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="K96" s="9">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D97" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H97" s="6">
+        <v>15</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="61"/>
+        <v>15</v>
+      </c>
+      <c r="J97" s="8">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="K97" s="9">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="5">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D98" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98" s="6">
+        <v>10</v>
+      </c>
+      <c r="I98" s="6">
+        <f t="shared" si="61"/>
+        <v>10</v>
+      </c>
+      <c r="J98" s="8">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="K98" s="9">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D99" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G99" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H99" s="6">
+        <v>15</v>
+      </c>
+      <c r="I99" s="6">
+        <f t="shared" ref="I99:I102" si="64">H99</f>
+        <v>15</v>
+      </c>
+      <c r="J99" s="8">
+        <f t="shared" ref="J99:J102" si="65">H99-I99</f>
+        <v>0</v>
+      </c>
+      <c r="K99" s="9">
+        <f t="shared" ref="K99:K102" si="66">(I99/(I99+J99))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="5">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D100" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H100" s="6">
+        <v>25</v>
+      </c>
+      <c r="I100" s="6">
+        <f t="shared" si="64"/>
+        <v>25</v>
+      </c>
+      <c r="J100" s="8">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="9">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D101" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H101" s="6">
+        <v>10</v>
+      </c>
+      <c r="I101" s="6">
+        <f t="shared" si="64"/>
+        <v>10</v>
+      </c>
+      <c r="J101" s="8">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="K101" s="9">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="5">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H102" s="6">
+        <v>25</v>
+      </c>
+      <c r="I102" s="6">
+        <f t="shared" si="64"/>
+        <v>25</v>
+      </c>
+      <c r="J102" s="8">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="K102" s="9">
+        <f t="shared" si="66"/>
         <v>1</v>
       </c>
     </row>
@@ -5814,13 +6405,13 @@
     </row>
     <row r="3" spans="1:4" ht="12.75">
       <c r="A3" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="30">
-        <v>8400</v>
+        <v>2057</v>
       </c>
       <c r="C3" s="31">
-        <v>8400</v>
+        <v>2057</v>
       </c>
       <c r="D3" s="32">
         <v>0</v>
@@ -5828,23 +6419,23 @@
     </row>
     <row r="4" spans="1:4" ht="12.75">
       <c r="A4" s="27" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="34"/>
       <c r="D4" s="35"/>
     </row>
     <row r="5" spans="1:4" ht="12.75">
-      <c r="A5" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="36">
-        <v>8400</v>
-      </c>
-      <c r="C5" s="37">
-        <v>8400</v>
-      </c>
-      <c r="D5" s="38">
+      <c r="A5" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="37">
+        <v>2057</v>
+      </c>
+      <c r="C5" s="38">
+        <v>2057</v>
+      </c>
+      <c r="D5" s="39">
         <v>0</v>
       </c>
     </row>
@@ -5899,11 +6490,11 @@
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="13">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>1917</v>
+        <v>2057</v>
       </c>
       <c r="B2" s="13">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>1917</v>
+        <v>2057</v>
       </c>
       <c r="C2" s="13">
         <f>SUM('liste des taches'!J:J)</f>
@@ -5940,7 +6531,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1">
@@ -5971,6 +6562,9 @@
       <c r="I1" s="19">
         <v>46159</v>
       </c>
+      <c r="J1" s="19">
+        <v>46160</v>
+      </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1">
       <c r="A2" s="20">
@@ -5986,7 +6580,7 @@
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="16"/>
-      <c r="K2" s="39"/>
+      <c r="K2" s="29"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1">
       <c r="A3" s="20">
@@ -6843,7 +7437,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13">
-        <f t="shared" ref="B67:B92" si="1">SUM(C67:P67)</f>
+        <f t="shared" ref="B67:B102" si="1">SUM(C67:P67)</f>
         <v>15</v>
       </c>
       <c r="F67">
@@ -7020,7 +7614,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" customHeight="1">
+    <row r="81" spans="1:10" ht="15.75" customHeight="1">
       <c r="A81" s="20">
         <v>80</v>
       </c>
@@ -7033,7 +7627,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1">
+    <row r="82" spans="1:10" ht="15.75" customHeight="1">
       <c r="A82" s="20">
         <v>81</v>
       </c>
@@ -7046,7 +7640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" customHeight="1">
+    <row r="83" spans="1:10" ht="15.75" customHeight="1">
       <c r="A83" s="20">
         <v>82</v>
       </c>
@@ -7059,7 +7653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1">
+    <row r="84" spans="1:10" ht="15.75" customHeight="1">
       <c r="A84" s="20">
         <v>83</v>
       </c>
@@ -7072,7 +7666,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" customHeight="1">
+    <row r="85" spans="1:10" ht="15.75" customHeight="1">
       <c r="A85" s="20">
         <v>84</v>
       </c>
@@ -7085,7 +7679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" customHeight="1">
+    <row r="86" spans="1:10" ht="15.75" customHeight="1">
       <c r="A86" s="20">
         <v>85</v>
       </c>
@@ -7098,7 +7692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1">
+    <row r="87" spans="1:10" ht="15.75" customHeight="1">
       <c r="A87" s="20">
         <v>86</v>
       </c>
@@ -7111,7 +7705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" customHeight="1">
+    <row r="88" spans="1:10" ht="15.75" customHeight="1">
       <c r="A88" s="20">
         <v>87</v>
       </c>
@@ -7124,7 +7718,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1">
+    <row r="89" spans="1:10" ht="15.75" customHeight="1">
       <c r="A89" s="20">
         <v>88</v>
       </c>
@@ -7137,7 +7731,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" customHeight="1">
+    <row r="90" spans="1:10" ht="15.75" customHeight="1">
       <c r="A90" s="20">
         <v>89</v>
       </c>
@@ -7150,7 +7744,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1">
+    <row r="91" spans="1:10" ht="15.75" customHeight="1">
       <c r="A91" s="20">
         <v>90</v>
       </c>
@@ -7163,7 +7757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" customHeight="1">
+    <row r="92" spans="1:10" ht="15.75" customHeight="1">
       <c r="A92" s="20">
         <v>91</v>
       </c>
@@ -7176,10 +7770,134 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1">
-      <c r="I93">
-        <f>'liste des taches'!H93</f>
-        <v>15</v>
+    <row r="93" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A93" s="20">
+        <v>91</v>
+      </c>
+      <c r="B93" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J93">
+        <f>+'liste des taches'!H93</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A94" s="20">
+        <v>92</v>
+      </c>
+      <c r="B94" s="13">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J94">
+        <f>+'liste des taches'!H94</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A95" s="20">
+        <v>93</v>
+      </c>
+      <c r="B95" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J95">
+        <f>+'liste des taches'!H95</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A96" s="20">
+        <v>94</v>
+      </c>
+      <c r="B96" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J96">
+        <f>+'liste des taches'!H96</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A97" s="20">
+        <v>95</v>
+      </c>
+      <c r="B97" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J97">
+        <f>+'liste des taches'!H97</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A98" s="20">
+        <v>96</v>
+      </c>
+      <c r="B98" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J98">
+        <f>+'liste des taches'!H98</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A99" s="20">
+        <v>97</v>
+      </c>
+      <c r="B99" s="13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J99">
+        <f>+'liste des taches'!H99</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A100" s="20">
+        <v>98</v>
+      </c>
+      <c r="B100" s="13">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="J100">
+        <f>+'liste des taches'!H100</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A101" s="20">
+        <v>99</v>
+      </c>
+      <c r="B101" s="13">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J101">
+        <f>+'liste des taches'!H101</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A102" s="20">
+        <v>100</v>
+      </c>
+      <c r="B102" s="13">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="J102">
+        <f>+'liste des taches'!H102</f>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
